--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="120">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -67,10 +67,13 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>0-1-0</t>
-  </si>
-  <si>
-    <t>1-0-0</t>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,48 +169,48 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>nicholas spadaro</t>
+  </si>
+  <si>
     <t>Zachary Dillon</t>
   </si>
   <si>
-    <t>nicholas spadaro</t>
-  </si>
-  <si>
     <t>Kathy Dillon</t>
   </si>
   <si>
+    <t>Brendan Fanning</t>
+  </si>
+  <si>
+    <t>Sal Spadaro</t>
+  </si>
+  <si>
     <t>gabriella spadaro</t>
   </si>
   <si>
+    <t>Michael Dillon</t>
+  </si>
+  <si>
+    <t>Mikaela Mitcho</t>
+  </si>
+  <si>
     <t>Antonio  Spadaro</t>
   </si>
   <si>
-    <t>Brendan Fanning</t>
-  </si>
-  <si>
-    <t>Sal Spadaro</t>
+    <t>Marissa Rodriguez</t>
+  </si>
+  <si>
+    <t>Ryan Lesiak</t>
+  </si>
+  <si>
+    <t>Stephanie Mattei</t>
   </si>
   <si>
     <t>Josh Formola</t>
   </si>
   <si>
-    <t>Marissa Rodriguez</t>
-  </si>
-  <si>
-    <t>Stephanie Mattei</t>
-  </si>
-  <si>
-    <t>Mikaela Mitcho</t>
-  </si>
-  <si>
-    <t>Michael Dillon</t>
-  </si>
-  <si>
     <t>Lawrence Rosello</t>
   </si>
   <si>
-    <t>Ryan Lesiak</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -229,55 +235,67 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>10.6-3.3-0.1</t>
-  </si>
-  <si>
-    <t>11.1-2.9-0.1</t>
-  </si>
-  <si>
-    <t>10.8-3.1-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.2-0.1</t>
-  </si>
-  <si>
-    <t>3.4-10.5-0.1</t>
-  </si>
-  <si>
-    <t>2.2-11.7-0.1</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>12.9-1.1</t>
+  </si>
+  <si>
+    <t>11.6-2.3</t>
+  </si>
+  <si>
+    <t>10.9-3.0-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.2-0.2</t>
+  </si>
+  <si>
+    <t>6.8-7.0-0.2</t>
+  </si>
+  <si>
+    <t>6.6-7.4-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.3-0.2</t>
+  </si>
+  <si>
+    <t>4.5-9.4-0.1</t>
+  </si>
+  <si>
+    <t>3.7-10.2-0.1</t>
+  </si>
+  <si>
+    <t>3.0-10.9-0.1</t>
+  </si>
+  <si>
+    <t>1.4-12.5-0.1</t>
+  </si>
+  <si>
+    <t>13-1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>10-4</t>
+    <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
@@ -286,19 +304,19 @@
     <t>7-7</t>
   </si>
   <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
     <t>3-11</t>
   </si>
   <si>
-    <t>2-12</t>
+    <t>1-13</t>
   </si>
   <si>
     <t>Owners</t>
@@ -310,7 +328,40 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -750,16 +801,16 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
@@ -780,7 +831,7 @@
         <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -797,16 +848,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -835,46 +886,46 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -888,19 +939,19 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
@@ -915,13 +966,13 @@
         <v>14</v>
       </c>
       <c r="M5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -932,43 +983,43 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1032,16 +1083,16 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -1076,19 +1127,19 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -1109,7 +1160,7 @@
         <v>15</v>
       </c>
       <c r="O9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1120,43 +1171,43 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
         <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1167,22 +1218,22 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -1197,13 +1248,13 @@
         <v>14</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1214,22 +1265,22 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
@@ -1244,13 +1295,13 @@
         <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1276,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -1305,46 +1356,46 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1355,22 +1406,22 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -1385,13 +1436,13 @@
         <v>14</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1401,30 +1452,108 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>-9</v>
+      </c>
+      <c r="F2">
+        <v>-4</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>-3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1439,13 +1568,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1456,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.07142857142857142</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1467,10 +1596,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>0.1428571428571428</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1481,13 +1610,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>0.2142857142857143</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1495,10 +1624,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0.2857142857142857</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1509,13 +1638,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1523,13 +1652,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>0.4285714285714285</v>
-      </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1537,10 +1666,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1551,13 +1680,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1565,13 +1694,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>0.5714285714285714</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1579,13 +1708,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.6428571428571429</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1596,10 +1725,10 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <v>0.7142857142857143</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1607,13 +1736,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>0.7857142857142857</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1621,13 +1750,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>0.8571428571428571</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1638,7 +1767,7 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>0.9285714285714286</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1656,16 +1785,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1676,7 +1805,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1690,16 +1819,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>0.9285714285714286</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D3">
-        <v>-0.0714285714285714</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1707,13 +1836,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>0.8571428571428571</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D4">
-        <v>-0.1428571428571429</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1724,13 +1853,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>0.7857142857142857</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D5">
-        <v>-0.2142857142857143</v>
+        <v>-0.8571428571428572</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1741,16 +1870,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0.6428571428571429</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D6">
-        <v>-0.3571428571428571</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1761,10 +1890,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>0.6428571428571429</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="D7">
-        <v>0.6428571428571429</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -1775,16 +1904,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>-0.4285714285714286</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1792,16 +1921,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1809,13 +1938,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.3571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D10">
-        <v>0.3571428571428572</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -1826,13 +1955,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>0.2857142857142857</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D11">
-        <v>0.2857142857142857</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1843,16 +1972,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>0.2142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D12">
-        <v>0.2142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1863,10 +1992,10 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="D13">
-        <v>0.1428571428571428</v>
+        <v>-0.5</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -1877,16 +2006,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>0.07142857142857142</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D14">
-        <v>0.07142857142857142</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1897,13 +2026,13 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1918,81 +2047,81 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>23.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C2">
-        <v>26.5</v>
+        <v>13.6</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="E2">
-        <v>13.4</v>
+        <v>0.3</v>
       </c>
       <c r="F2">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2001,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2013,39 +2142,39 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>41.8</v>
+        <v>7.6</v>
       </c>
       <c r="C3">
-        <v>26.8</v>
+        <v>55.9</v>
       </c>
       <c r="D3">
-        <v>15.5</v>
+        <v>32.3</v>
       </c>
       <c r="E3">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2063,39 +2192,39 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>26.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C4">
-        <v>29.2</v>
+        <v>27.5</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>45.4</v>
       </c>
       <c r="E4">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="F4">
         <v>4.8</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -2113,45 +2242,45 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>99.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B5">
+        <v>0.1</v>
+      </c>
+      <c r="C5">
+        <v>2.3</v>
+      </c>
+      <c r="D5">
+        <v>9.5</v>
+      </c>
+      <c r="E5">
+        <v>37.5</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>13.5</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
+      </c>
+      <c r="I5">
         <v>4.1</v>
       </c>
-      <c r="C5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D5">
-        <v>17.4</v>
-      </c>
-      <c r="E5">
-        <v>22.8</v>
-      </c>
-      <c r="F5">
-        <v>21.9</v>
-      </c>
-      <c r="G5">
-        <v>11.6</v>
-      </c>
-      <c r="H5">
-        <v>6.5</v>
-      </c>
-      <c r="I5">
-        <v>5.2</v>
-      </c>
       <c r="J5">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -2163,45 +2292,45 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>97.7</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="D6">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>20.1</v>
       </c>
       <c r="F6">
-        <v>19.4</v>
+        <v>26.3</v>
       </c>
       <c r="G6">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="H6">
-        <v>16.6</v>
+        <v>12.6</v>
       </c>
       <c r="I6">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="L6">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M6">
         <v>0.1</v>
@@ -2210,48 +2339,48 @@
         <v>0.1</v>
       </c>
       <c r="O6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>10.8</v>
       </c>
       <c r="F7">
-        <v>20.2</v>
+        <v>18.5</v>
       </c>
       <c r="G7">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>13.7</v>
+        <v>19.6</v>
       </c>
       <c r="I7">
-        <v>8.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="J7">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="K7">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M7">
         <v>0.2</v>
@@ -2263,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>91</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2271,154 +2400,154 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="F8">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="G8">
-        <v>13.1</v>
+        <v>16.8</v>
       </c>
       <c r="H8">
-        <v>20.3</v>
+        <v>21.8</v>
       </c>
       <c r="I8">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="J8">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="K8">
-        <v>11.3</v>
+        <v>8.6</v>
       </c>
       <c r="L8">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="M8">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="N8">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P8">
-        <v>66.2</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="E9">
-        <v>4.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F9">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="G9">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="H9">
-        <v>17.2</v>
+        <v>14.6</v>
       </c>
       <c r="I9">
-        <v>19.9</v>
+        <v>15</v>
       </c>
       <c r="J9">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="N9">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="P9">
-        <v>65.5</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="G10">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>18.2</v>
+        <v>14.2</v>
       </c>
       <c r="J10">
-        <v>20.1</v>
+        <v>15.3</v>
       </c>
       <c r="K10">
-        <v>15.1</v>
+        <v>17.2</v>
       </c>
       <c r="L10">
-        <v>9.9</v>
+        <v>11.6</v>
       </c>
       <c r="M10">
-        <v>6.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N10">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="P10">
-        <v>46.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2427,48 +2556,48 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H11">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>10.2</v>
+        <v>15.5</v>
       </c>
       <c r="J11">
-        <v>16</v>
+        <v>24.6</v>
       </c>
       <c r="K11">
-        <v>20.6</v>
+        <v>22.5</v>
       </c>
       <c r="L11">
-        <v>23.2</v>
+        <v>14.3</v>
       </c>
       <c r="M11">
-        <v>10.1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="O11">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="P11">
-        <v>22.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2480,40 +2609,40 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="K12">
-        <v>20.1</v>
+        <v>16.3</v>
       </c>
       <c r="L12">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="M12">
-        <v>16.5</v>
+        <v>18.6</v>
       </c>
       <c r="N12">
-        <v>9.300000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="O12">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="P12">
-        <v>13.4</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2536,39 +2665,39 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I13">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="K13">
-        <v>8.5</v>
+        <v>12.6</v>
       </c>
       <c r="L13">
-        <v>14</v>
+        <v>23.5</v>
       </c>
       <c r="M13">
-        <v>25</v>
+        <v>32.9</v>
       </c>
       <c r="N13">
-        <v>29.6</v>
+        <v>21.4</v>
       </c>
       <c r="O13">
-        <v>16.8</v>
+        <v>2.2</v>
       </c>
       <c r="P13">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2589,31 +2718,31 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I14">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="K14">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="M14">
-        <v>27.5</v>
+        <v>26.2</v>
       </c>
       <c r="N14">
-        <v>29.2</v>
+        <v>39.8</v>
       </c>
       <c r="O14">
-        <v>17.1</v>
+        <v>13</v>
       </c>
       <c r="P14">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2636,34 +2765,34 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>0.1</v>
       </c>
-      <c r="J15">
-        <v>0.6</v>
-      </c>
-      <c r="K15">
-        <v>1.9</v>
-      </c>
       <c r="L15">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="M15">
-        <v>10.2</v>
+        <v>2.3</v>
       </c>
       <c r="N15">
-        <v>22.9</v>
+        <v>15.6</v>
       </c>
       <c r="O15">
-        <v>59.8</v>
+        <v>81.3</v>
       </c>
       <c r="P15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2673,169 +2802,214 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3">
+        <v>99.8</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>92</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
         <v>99.7</v>
       </c>
-      <c r="C3">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>99.8</v>
-      </c>
-      <c r="C4">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>97.2</v>
+        <v>43.7</v>
       </c>
       <c r="C5">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>97.7</v>
+      </c>
+      <c r="D5">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>91.10000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C6">
-        <v>92.10000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="D6">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>88.8</v>
+        <v>72</v>
       </c>
       <c r="C7">
-        <v>91.60000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="D7">
+        <v>86.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B8">
-        <v>70.39999999999999</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>65.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>64.7</v>
+      </c>
+      <c r="D8">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>72</v>
+        <v>99.8</v>
       </c>
       <c r="C9">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>63.3</v>
+      </c>
+      <c r="D9">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>46</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C10">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>42.9</v>
+      </c>
+      <c r="D10">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>32.5</v>
+      </c>
+      <c r="D11">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>2.3</v>
+      </c>
+      <c r="C12">
+        <v>10.6</v>
+      </c>
+      <c r="D12">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>4.8</v>
+      </c>
+      <c r="D13">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B11">
-        <v>19.4</v>
-      </c>
-      <c r="C11">
-        <v>23.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12">
-        <v>10.8</v>
-      </c>
-      <c r="C12">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13">
-        <v>2.6</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B14">
-        <v>1.9</v>
+        <v>18.3</v>
       </c>
       <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="D14">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C15">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2850,28 +3024,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2879,28 +3053,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>73.22</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>116.42</v>
+        <v>116.73</v>
       </c>
       <c r="G2">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2908,28 +3082,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>86.08</v>
+        <v>77.89</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>116.63</v>
+        <v>114.66</v>
       </c>
       <c r="G3">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2940,25 +3114,25 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>108.66</v>
+        <v>109.03</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
       <c r="F4">
-        <v>113.36</v>
+        <v>112.69</v>
       </c>
       <c r="G4">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2966,28 +3140,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>111.56</v>
+        <v>98.63</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>116.73</v>
+        <v>115.18</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2995,28 +3169,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>108.12</v>
+        <v>103.42</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6">
-        <v>111.07</v>
+        <v>114.01</v>
       </c>
       <c r="G6">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3024,28 +3198,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>108.6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>110.73</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
         <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>130.62</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>114.93</v>
-      </c>
-      <c r="G7">
-        <v>0.538</v>
-      </c>
-      <c r="H7">
-        <v>0.2</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3053,28 +3227,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>95.95999999999999</v>
+        <v>108.43</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8">
-        <v>112.8</v>
+        <v>112.45</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H8">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3082,28 +3256,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>148.16</v>
+        <v>90.02</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>113.23</v>
+        <v>112.61</v>
       </c>
       <c r="G9">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H9">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3111,28 +3285,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>120.5</v>
+        <v>120.55</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>110.76</v>
+        <v>105.64</v>
       </c>
       <c r="G10">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H10">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3140,28 +3314,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>83.06</v>
+        <v>135.92</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>111.54</v>
+        <v>107.88</v>
       </c>
       <c r="G11">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3169,28 +3343,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12">
-        <v>99.94</v>
+        <v>113.46</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
       </c>
       <c r="F12">
-        <v>110.62</v>
+        <v>106.61</v>
       </c>
       <c r="G12">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>-0.5</v>
+        <v>-2.2</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3198,28 +3372,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13">
-        <v>142.64</v>
+        <v>95.08</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>110.89</v>
+        <v>105.85</v>
       </c>
       <c r="G13">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H13">
-        <v>-0.6</v>
+        <v>-2.8</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3227,28 +3401,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14">
-        <v>141.26</v>
+        <v>150.58</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
       </c>
       <c r="F14">
-        <v>107.28</v>
+        <v>104.82</v>
       </c>
       <c r="G14">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H14">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="I14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3256,28 +3430,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D15">
-        <v>122.76</v>
+        <v>137.82</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>106.29</v>
+        <v>102.85</v>
       </c>
       <c r="G15">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H15">
-        <v>-1.5</v>
+        <v>-3.2</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3292,205 +3466,205 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>142.64</v>
+        <v>150.58</v>
       </c>
       <c r="E2">
-        <v>142.64</v>
+        <v>301.16</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
-        <v>148.16</v>
+        <v>137.82</v>
       </c>
       <c r="E3">
-        <v>148.16</v>
+        <v>275.64</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>141.26</v>
+        <v>135.92</v>
       </c>
       <c r="E4">
-        <v>141.26</v>
+        <v>271.84</v>
       </c>
       <c r="F4">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>130.62</v>
+        <v>120.55</v>
       </c>
       <c r="E5">
-        <v>130.62</v>
+        <v>241.1</v>
       </c>
       <c r="F5">
-        <v>97.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>120.5</v>
+        <v>113.46</v>
       </c>
       <c r="E6">
-        <v>120.5</v>
+        <v>226.92</v>
       </c>
       <c r="F6">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>122.76</v>
+        <v>109.03</v>
       </c>
       <c r="E7">
-        <v>122.76</v>
+        <v>218.06</v>
       </c>
       <c r="F7">
+        <v>89.3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" t="s">
         <v>91</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3498,144 +3672,144 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>111.56</v>
+        <v>108.6</v>
       </c>
       <c r="E8">
-        <v>111.56</v>
+        <v>217.2</v>
       </c>
       <c r="F8">
-        <v>66.2</v>
+        <v>71.89999999999999</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>108.66</v>
+        <v>108.43</v>
       </c>
       <c r="E9">
-        <v>108.66</v>
+        <v>216.86</v>
       </c>
       <c r="F9">
-        <v>65.5</v>
+        <v>61.1</v>
       </c>
       <c r="G9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>108.12</v>
+        <v>98.63</v>
       </c>
       <c r="E10">
-        <v>108.12</v>
+        <v>197.26</v>
       </c>
       <c r="F10">
-        <v>46.8</v>
+        <v>41.6</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>99.94</v>
+        <v>103.42</v>
       </c>
       <c r="E11">
-        <v>99.94</v>
+        <v>206.84</v>
       </c>
       <c r="F11">
-        <v>22.8</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>95.95999999999999</v>
+        <v>95.08</v>
       </c>
       <c r="E12">
-        <v>95.95999999999999</v>
+        <v>190.16</v>
       </c>
       <c r="F12">
-        <v>13.4</v>
+        <v>14.2</v>
       </c>
       <c r="G12">
-        <v>4.100000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3643,57 +3817,57 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D13">
-        <v>86.08</v>
+        <v>93.28999999999999</v>
       </c>
       <c r="E13">
-        <v>86.08</v>
+        <v>186.58</v>
       </c>
       <c r="F13">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G13">
-        <v>16.8</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>83.06</v>
+        <v>90.02</v>
       </c>
       <c r="E14">
-        <v>83.06</v>
+        <v>180.04</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G14">
-        <v>17.1</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3701,28 +3875,28 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>73.22</v>
+        <v>77.89</v>
       </c>
       <c r="E15">
-        <v>73.22</v>
+        <v>155.78</v>
       </c>
       <c r="F15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>59.8</v>
+        <v>81.3</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3737,19 +3911,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3760,16 +3934,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3777,19 +3951,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3797,19 +3971,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>57</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="F4">
-        <v>0</v>
+      <c r="F4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3817,19 +3991,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3837,19 +4011,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3857,19 +4031,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3877,19 +4051,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3897,19 +4071,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="F9">
-        <v>0</v>
+      <c r="F9" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3923,13 +4097,13 @@
         <v>52</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
-      <c r="F10">
-        <v>0</v>
+      <c r="F10" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3937,19 +4111,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3957,19 +4131,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3980,16 +4154,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
       </c>
-      <c r="F13">
-        <v>0</v>
+      <c r="F13" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4000,16 +4174,16 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
       </c>
-      <c r="F14">
-        <v>0</v>
+      <c r="F14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4020,16 +4194,16 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>-7</v>
+        <v>-13</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4039,18 +4213,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>112</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4058,87 +4235,111 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
       <c r="C8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>-1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -4146,32 +4347,41 @@
         <v>-1</v>
       </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>-3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>-4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>-1</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>-3</v>
-      </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>-4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -4179,10 +4389,13 @@
         <v>-4</v>
       </c>
       <c r="C13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>-9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -4190,10 +4403,13 @@
         <v>-5</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>-9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
@@ -4201,7 +4417,10 @@
         <v>-7</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="119">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -244,10 +244,10 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>12.9-1.1</t>
-  </si>
-  <si>
-    <t>11.6-2.3</t>
+    <t>12.8-1.2</t>
+  </si>
+  <si>
+    <t>11.5-2.4</t>
   </si>
   <si>
     <t>10.9-3.0-0.1</t>
@@ -262,22 +262,22 @@
     <t>7.6-6.2-0.2</t>
   </si>
   <si>
-    <t>6.8-7.0-0.2</t>
-  </si>
-  <si>
-    <t>6.6-7.4-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.3-0.2</t>
-  </si>
-  <si>
-    <t>4.5-9.4-0.1</t>
-  </si>
-  <si>
-    <t>3.7-10.2-0.1</t>
+    <t>6.8-7.1-0.2</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.0-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.2-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
+  </si>
+  <si>
+    <t>3.8-10.2-0.1</t>
   </si>
   <si>
     <t>3.0-10.9-0.1</t>
@@ -302,9 +302,6 @@
   </si>
   <si>
     <t>7-7</t>
-  </si>
-  <si>
-    <t>5-9</t>
   </si>
   <si>
     <t>6-8</t>
@@ -1457,25 +1454,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2100,19 +2097,19 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>83.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="C2">
-        <v>13.6</v>
+        <v>14.6</v>
       </c>
       <c r="D2">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="E2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2150,19 +2147,19 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="C3">
         <v>55.9</v>
       </c>
       <c r="D3">
-        <v>32.3</v>
+        <v>30.7</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="F3">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2200,34 +2197,34 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>8.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="C4">
-        <v>27.5</v>
+        <v>26.2</v>
       </c>
       <c r="D4">
-        <v>45.4</v>
+        <v>47</v>
       </c>
       <c r="E4">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="F4">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="G4">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2242,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2253,25 +2250,25 @@
         <v>0.1</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="E5">
-        <v>37.5</v>
+        <v>38.7</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22.4</v>
       </c>
       <c r="G5">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J5">
         <v>1.9</v>
@@ -2280,10 +2277,10 @@
         <v>0.8</v>
       </c>
       <c r="L5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2292,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>97.09999999999999</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2303,46 +2300,46 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="E6">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="F6">
-        <v>26.3</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>18.8</v>
+        <v>21.7</v>
       </c>
       <c r="H6">
-        <v>12.6</v>
+        <v>13.7</v>
       </c>
       <c r="I6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="L6">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>91.7</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2350,49 +2347,49 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
         <v>0.2</v>
       </c>
       <c r="D7">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="E7">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F7">
-        <v>18.5</v>
+        <v>17.8</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="H7">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="I7">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="J7">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="N7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>89.3</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2403,46 +2400,46 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="F8">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G8">
-        <v>16.8</v>
+        <v>13.6</v>
       </c>
       <c r="H8">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>19.9</v>
       </c>
       <c r="J8">
-        <v>14.3</v>
+        <v>16.9</v>
       </c>
       <c r="K8">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="L8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M8">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="N8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>71.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2450,49 +2447,49 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="E9">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="F9">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="G9">
-        <v>11.6</v>
+        <v>13.5</v>
       </c>
       <c r="H9">
-        <v>14.6</v>
+        <v>11.9</v>
       </c>
       <c r="I9">
-        <v>15</v>
+        <v>15.7</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="K9">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="L9">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="O9">
         <v>0.3</v>
       </c>
       <c r="P9">
-        <v>61.1</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2500,49 +2497,49 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G10">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="I10">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="J10">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="K10">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
       <c r="L10">
-        <v>11.6</v>
+        <v>12.9</v>
       </c>
       <c r="M10">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="P10">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2556,43 +2553,43 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G11">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="I11">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="J11">
+        <v>22.9</v>
+      </c>
+      <c r="K11">
         <v>24.6</v>
       </c>
-      <c r="K11">
-        <v>22.5</v>
-      </c>
       <c r="L11">
-        <v>14.3</v>
+        <v>11.9</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="N11">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P11">
-        <v>30</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2609,40 +2606,40 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G12">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="I12">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="J12">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
       <c r="K12">
-        <v>16.3</v>
+        <v>15.1</v>
       </c>
       <c r="L12">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="M12">
-        <v>18.6</v>
+        <v>25.2</v>
       </c>
       <c r="N12">
-        <v>14.1</v>
+        <v>12.9</v>
       </c>
       <c r="O12">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <v>14.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2665,34 +2662,34 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H13">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="I13">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K13">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="L13">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="M13">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="N13">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="O13">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2718,31 +2715,31 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="K14">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
       <c r="M14">
-        <v>26.2</v>
+        <v>23.6</v>
       </c>
       <c r="N14">
-        <v>39.8</v>
+        <v>42.9</v>
       </c>
       <c r="O14">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="P14">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2777,19 +2774,19 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L15">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M15">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="N15">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="O15">
-        <v>81.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2821,7 +2818,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2835,7 +2832,7 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2849,13 +2846,13 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>92</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2863,13 +2860,13 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>43.7</v>
+        <v>45.7</v>
       </c>
       <c r="C5">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="D5">
-        <v>98.2</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2877,13 +2874,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>88.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="C6">
-        <v>95.19999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="D6">
-        <v>94.09999999999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2891,13 +2888,13 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>72</v>
+        <v>75.2</v>
       </c>
       <c r="C7">
-        <v>87.40000000000001</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="D7">
-        <v>86.7</v>
+        <v>89.60000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2905,13 +2902,13 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>64.7</v>
+        <v>65.8</v>
       </c>
       <c r="D8">
-        <v>69.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2919,13 +2916,13 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>63.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D9">
-        <v>61.6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2933,13 +2930,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="C10">
-        <v>42.9</v>
+        <v>39.8</v>
       </c>
       <c r="D10">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2947,13 +2944,13 @@
         <v>0</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C11">
+        <v>31.5</v>
+      </c>
+      <c r="D11">
         <v>32.5</v>
-      </c>
-      <c r="D11">
-        <v>32.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2961,13 +2958,13 @@
         <v>3</v>
       </c>
       <c r="B12">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="C12">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="D12">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2975,13 +2972,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="C13">
-        <v>4.8</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="D13">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2989,13 +2986,13 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>18.3</v>
+        <v>17.1</v>
       </c>
       <c r="C14">
+        <v>1.2</v>
+      </c>
+      <c r="D14">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="D14">
-        <v>1.2</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3003,7 +3000,7 @@
         <v>8</v>
       </c>
       <c r="B15">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3568,7 +3565,7 @@
         <v>271.84</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3597,7 +3594,7 @@
         <v>241.1</v>
       </c>
       <c r="F5">
-        <v>97.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3626,7 +3623,7 @@
         <v>226.92</v>
       </c>
       <c r="F6">
-        <v>91.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3655,7 +3652,7 @@
         <v>218.06</v>
       </c>
       <c r="F7">
-        <v>89.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3684,10 +3681,10 @@
         <v>217.2</v>
       </c>
       <c r="F8">
-        <v>71.89999999999999</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="G8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
         <v>79</v>
@@ -3713,7 +3710,7 @@
         <v>216.86</v>
       </c>
       <c r="F9">
-        <v>61.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G9">
         <v>0.3</v>
@@ -3742,10 +3739,10 @@
         <v>197.26</v>
       </c>
       <c r="F10">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
       <c r="G10">
-        <v>0.8999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="s">
         <v>81</v>
@@ -3771,16 +3768,16 @@
         <v>206.84</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>33.7</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="s">
         <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3800,16 +3797,16 @@
         <v>190.16</v>
       </c>
       <c r="F12">
-        <v>14.2</v>
+        <v>10.8</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
         <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3829,16 +3826,16 @@
         <v>186.58</v>
       </c>
       <c r="F13">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G13">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H13" t="s">
         <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3858,16 +3855,16 @@
         <v>180.04</v>
       </c>
       <c r="F14">
-        <v>0.8999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G14">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="H14" t="s">
         <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3890,13 +3887,13 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>81.3</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="H15" t="s">
         <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3914,16 +3911,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3943,7 +3940,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3963,7 +3960,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3983,7 +3980,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4003,7 +4000,7 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4023,7 +4020,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4043,7 +4040,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4063,7 +4060,7 @@
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4083,7 +4080,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4103,7 +4100,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4123,7 +4120,7 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4143,7 +4140,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4163,7 +4160,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4183,7 +4180,7 @@
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4203,7 +4200,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -4218,13 +4215,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4238,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4252,7 +4249,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4266,7 +4263,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4280,7 +4277,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4294,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4308,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4322,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4336,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4350,7 +4347,7 @@
         <v>-3</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4364,7 +4361,7 @@
         <v>-4</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4378,7 +4375,7 @@
         <v>-4</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4392,7 +4389,7 @@
         <v>-9</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4406,7 +4403,7 @@
         <v>-9</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4420,7 +4417,7 @@
         <v>-13</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="119">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -67,13 +67,16 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +151,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -172,33 +178,33 @@
     <t>nicholas spadaro</t>
   </si>
   <si>
+    <t>Brendan Fanning</t>
+  </si>
+  <si>
     <t>Zachary Dillon</t>
   </si>
   <si>
     <t>Kathy Dillon</t>
   </si>
   <si>
-    <t>Brendan Fanning</t>
+    <t>gabriella spadaro</t>
   </si>
   <si>
     <t>Sal Spadaro</t>
   </si>
   <si>
-    <t>gabriella spadaro</t>
+    <t>Antonio  Spadaro</t>
   </si>
   <si>
     <t>Michael Dillon</t>
   </si>
   <si>
+    <t>Marissa Rodriguez</t>
+  </si>
+  <si>
     <t>Mikaela Mitcho</t>
   </si>
   <si>
-    <t>Antonio  Spadaro</t>
-  </si>
-  <si>
-    <t>Marissa Rodriguez</t>
-  </si>
-  <si>
     <t>Ryan Lesiak</t>
   </si>
   <si>
@@ -235,55 +241,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>12.8-1.2</t>
-  </si>
-  <si>
-    <t>11.5-2.4</t>
-  </si>
-  <si>
-    <t>10.9-3.0-0.1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>12.3-1.7-0.1</t>
+  </si>
+  <si>
+    <t>11.3-2.6-0.1</t>
+  </si>
+  <si>
+    <t>11.1-2.8-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
   </si>
   <si>
     <t>8.7-5.2-0.1</t>
   </si>
   <si>
-    <t>8.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>7.6-6.2-0.2</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.2</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>6.0-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.2-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.2-0.1</t>
-  </si>
-  <si>
-    <t>3.0-10.9-0.1</t>
-  </si>
-  <si>
-    <t>1.4-12.5-0.1</t>
+    <t>7.7-6.1-0.2</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.7-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9-0.1</t>
+  </si>
+  <si>
+    <t>3.8-10.1-0.1</t>
+  </si>
+  <si>
+    <t>2.3-11.6-0.1</t>
   </si>
   <si>
     <t>13-1</t>
@@ -301,19 +307,16 @@
     <t>8-6</t>
   </si>
   <si>
-    <t>7-7</t>
-  </si>
-  <si>
     <t>6-8</t>
   </si>
   <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>4-10</t>
   </si>
   <si>
-    <t>3-11</t>
-  </si>
-  <si>
-    <t>1-13</t>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -325,40 +328,37 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑2</t>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑7</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↓11</t>
+  </si>
+  <si>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -810,7 +810,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -842,22 +842,22 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
         <v>14</v>
@@ -866,7 +866,7 @@
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M3" t="s">
         <v>14</v>
@@ -875,7 +875,7 @@
         <v>15</v>
       </c>
       <c r="O3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -933,34 +933,34 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M5" t="s">
         <v>16</v>
@@ -969,7 +969,7 @@
         <v>16</v>
       </c>
       <c r="O5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -983,22 +983,22 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -1007,7 +1007,7 @@
         <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
         <v>16</v>
@@ -1016,7 +1016,7 @@
         <v>14</v>
       </c>
       <c r="O6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1030,10 +1030,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1045,7 +1045,7 @@
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
@@ -1054,7 +1054,7 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
         <v>15</v>
@@ -1063,7 +1063,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1092,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -1101,7 +1101,7 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
         <v>15</v>
@@ -1124,10 +1124,10 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -1139,7 +1139,7 @@
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
@@ -1148,7 +1148,7 @@
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M9" t="s">
         <v>15</v>
@@ -1157,7 +1157,7 @@
         <v>15</v>
       </c>
       <c r="O9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1168,34 +1168,34 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
         <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M10" t="s">
         <v>16</v>
@@ -1204,7 +1204,7 @@
         <v>16</v>
       </c>
       <c r="O10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1212,37 +1212,37 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M11" t="s">
         <v>16</v>
@@ -1251,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="O11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1259,37 +1259,37 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M12" t="s">
         <v>14</v>
@@ -1298,7 +1298,7 @@
         <v>14</v>
       </c>
       <c r="O12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1315,7 +1315,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -1327,7 +1327,7 @@
         <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
@@ -1336,7 +1336,7 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -1353,46 +1353,46 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1400,46 +1400,46 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1449,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1551,6 +1551,58 @@
       </c>
       <c r="H4" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>-15</v>
+      </c>
+      <c r="F5">
+        <v>-17</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1565,13 +1617,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1582,10 +1634,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.2142857142857143</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1596,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>0.3571428571428572</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1607,10 +1659,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>0.7857142857142857</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -1621,13 +1673,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>0.9285714285714286</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1638,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -1649,13 +1701,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1663,13 +1715,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1677,13 +1729,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1691,10 +1743,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.071428571428571</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1705,13 +1757,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>1.142857142857143</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1719,13 +1771,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>1.142857142857143</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1733,10 +1785,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>1.214285714285714</v>
+        <v>1.928571428571429</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1747,10 +1799,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>1.285714285714286</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
@@ -1761,13 +1813,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>1.857142857142857</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1782,16 +1834,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1802,10 +1854,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -1819,10 +1871,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>1.642857142857143</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
-        <v>0.6428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -1836,10 +1888,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>1.571428571428571</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="D4">
-        <v>-0.4285714285714286</v>
+        <v>-0.6428571428571428</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1850,16 +1902,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1.142857142857143</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>-0.8571428571428572</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1867,13 +1919,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1.142857142857143</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D6">
-        <v>0.1428571428571428</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -1884,13 +1936,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1.071428571428571</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D7">
-        <v>0.0714285714285714</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -1901,13 +1953,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -1918,16 +1970,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1935,16 +1987,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>0.9285714285714286</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="D10">
-        <v>-0.0714285714285714</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1952,16 +2004,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.7857142857142857</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D11">
-        <v>-0.2142857142857143</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1972,13 +2024,13 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D12">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1986,16 +2038,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>0.5</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D13">
-        <v>-0.5</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2003,16 +2055,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>0.4285714285714285</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D14">
-        <v>0.4285714285714285</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2023,13 +2075,13 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>0.2142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D15">
-        <v>0.2142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2044,52 +2096,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2097,19 +2149,19 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>82.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C2">
-        <v>14.6</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>2.8</v>
+        <v>10.3</v>
       </c>
       <c r="E2">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2147,25 +2199,25 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>7.9</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>55.9</v>
+        <v>43.5</v>
       </c>
       <c r="D3">
-        <v>30.7</v>
+        <v>27.9</v>
       </c>
       <c r="E3">
-        <v>4.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F3">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2197,34 +2249,34 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>26.2</v>
+        <v>27.4</v>
       </c>
       <c r="D4">
-        <v>47</v>
+        <v>37.4</v>
       </c>
       <c r="E4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="G4">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2239,48 +2291,48 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>99.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>4.1</v>
+      </c>
+      <c r="D5">
+        <v>12.1</v>
+      </c>
+      <c r="E5">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>24.5</v>
+      </c>
+      <c r="G5">
+        <v>13.2</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
+      </c>
+      <c r="I5">
+        <v>3.4</v>
+      </c>
+      <c r="J5">
+        <v>0.6</v>
+      </c>
+      <c r="K5">
         <v>0.1</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>8.1</v>
-      </c>
-      <c r="E5">
-        <v>38.7</v>
-      </c>
-      <c r="F5">
-        <v>22.4</v>
-      </c>
-      <c r="G5">
-        <v>12.9</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>4.5</v>
-      </c>
-      <c r="J5">
-        <v>1.9</v>
-      </c>
-      <c r="K5">
-        <v>0.8</v>
-      </c>
       <c r="L5">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2289,45 +2341,45 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>96.7</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C6">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D6">
-        <v>5.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E6">
-        <v>18.1</v>
+        <v>23.3</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="G6">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>13.7</v>
+        <v>11.9</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="L6">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2339,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>92.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2350,201 +2402,201 @@
         <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
         <v>1.6</v>
       </c>
       <c r="E7">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="F7">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="G7">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="H7">
-        <v>19.4</v>
+        <v>22.7</v>
       </c>
       <c r="I7">
-        <v>12.2</v>
+        <v>13.8</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="L7">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="M7">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>86.59999999999999</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="E8">
-        <v>3.8</v>
+        <v>6.9</v>
       </c>
       <c r="F8">
-        <v>9.800000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="G8">
-        <v>13.6</v>
+        <v>23.6</v>
       </c>
       <c r="H8">
-        <v>22.7</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>19.9</v>
+        <v>14.4</v>
       </c>
       <c r="J8">
-        <v>16.9</v>
+        <v>7.3</v>
       </c>
       <c r="K8">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="L8">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="M8">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>70.40000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="F9">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="G9">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <v>11.9</v>
+        <v>17.8</v>
       </c>
       <c r="I9">
-        <v>15.7</v>
+        <v>28.6</v>
       </c>
       <c r="J9">
-        <v>11.8</v>
+        <v>19.1</v>
       </c>
       <c r="K9">
-        <v>11.9</v>
+        <v>8.6</v>
       </c>
       <c r="L9">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="N9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O9">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="P9">
-        <v>64.09999999999999</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="F10">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="H10">
-        <v>10.9</v>
+        <v>7.4</v>
       </c>
       <c r="I10">
-        <v>14.4</v>
+        <v>16.9</v>
       </c>
       <c r="J10">
-        <v>15.6</v>
+        <v>23.2</v>
       </c>
       <c r="K10">
-        <v>16.5</v>
+        <v>19.4</v>
       </c>
       <c r="L10">
-        <v>12.9</v>
+        <v>14.2</v>
       </c>
       <c r="M10">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="O10">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="P10">
-        <v>42.3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2553,43 +2605,43 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>0.1</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
       <c r="F11">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="H11">
+        <v>2.8</v>
+      </c>
+      <c r="I11">
+        <v>5.6</v>
+      </c>
+      <c r="J11">
+        <v>11.8</v>
+      </c>
+      <c r="K11">
+        <v>17.8</v>
+      </c>
+      <c r="L11">
+        <v>17.4</v>
+      </c>
+      <c r="M11">
+        <v>18.4</v>
+      </c>
+      <c r="N11">
+        <v>16.1</v>
+      </c>
+      <c r="O11">
         <v>9.4</v>
       </c>
-      <c r="I11">
-        <v>16.8</v>
-      </c>
-      <c r="J11">
-        <v>22.9</v>
-      </c>
-      <c r="K11">
-        <v>24.6</v>
-      </c>
-      <c r="L11">
-        <v>11.9</v>
-      </c>
-      <c r="M11">
-        <v>5.4</v>
-      </c>
-      <c r="N11">
-        <v>1.3</v>
-      </c>
-      <c r="O11">
-        <v>0.2</v>
-      </c>
       <c r="P11">
-        <v>33.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2603,48 +2655,48 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F12">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="K12">
-        <v>15.1</v>
+        <v>16.5</v>
       </c>
       <c r="L12">
-        <v>23.2</v>
+        <v>17.4</v>
       </c>
       <c r="M12">
-        <v>25.2</v>
+        <v>18.3</v>
       </c>
       <c r="N12">
-        <v>12.9</v>
+        <v>17.3</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>10.3</v>
       </c>
       <c r="P12">
-        <v>10.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2656,45 +2708,45 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G13">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H13">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J13">
-        <v>5.1</v>
+        <v>11.2</v>
       </c>
       <c r="K13">
-        <v>11.1</v>
+        <v>15.5</v>
       </c>
       <c r="L13">
-        <v>23.9</v>
+        <v>17.5</v>
       </c>
       <c r="M13">
-        <v>32.2</v>
+        <v>17.8</v>
       </c>
       <c r="N13">
-        <v>22.3</v>
+        <v>20.7</v>
       </c>
       <c r="O13">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2712,34 +2764,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H14">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="I14">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J14">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="L14">
-        <v>12.7</v>
+        <v>21.6</v>
       </c>
       <c r="M14">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="N14">
-        <v>42.9</v>
+        <v>20.3</v>
       </c>
       <c r="O14">
-        <v>11.7</v>
+        <v>6.2</v>
       </c>
       <c r="P14">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2765,31 +2817,31 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K15">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="L15">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="M15">
-        <v>2.2</v>
+        <v>9.4</v>
       </c>
       <c r="N15">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="O15">
-        <v>82.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -2799,26 +2851,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2826,8 +2881,11 @@
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2840,13 +2898,16 @@
       <c r="D3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>93.60000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2854,159 +2915,195 @@
       <c r="D4">
         <v>99.90000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="C5">
+        <v>67.7</v>
+      </c>
+      <c r="D5">
+        <v>98.7</v>
+      </c>
+      <c r="E5">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>45.7</v>
-      </c>
-      <c r="C5">
-        <v>97.2</v>
-      </c>
-      <c r="D5">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B6">
-        <v>88.90000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="C6">
-        <v>94.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D6">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E6">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>75.2</v>
+        <v>71.2</v>
       </c>
       <c r="C7">
-        <v>89.60000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D7">
-        <v>89.60000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>92.30000000000001</v>
+      </c>
+      <c r="E7">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>38</v>
+      </c>
+      <c r="D8">
+        <v>92.2</v>
+      </c>
+      <c r="E8">
+        <v>90.10000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>95.3</v>
+      </c>
+      <c r="C9">
+        <v>94.89999999999999</v>
+      </c>
+      <c r="D9">
+        <v>68.10000000000001</v>
+      </c>
+      <c r="E9">
+        <v>68.30000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8">
-        <v>69</v>
-      </c>
-      <c r="C8">
-        <v>65.8</v>
-      </c>
-      <c r="D8">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="B10">
+        <v>70.5</v>
+      </c>
+      <c r="C10">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="D10">
+        <v>23.6</v>
+      </c>
+      <c r="E10">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>97.7</v>
-      </c>
-      <c r="C10">
-        <v>39.8</v>
-      </c>
-      <c r="D10">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B11">
-        <v>9.800000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C11">
-        <v>31.5</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>10.2</v>
+      </c>
+      <c r="E11">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B12">
-        <v>1.4</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C12">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="D12">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>6.3</v>
+      </c>
+      <c r="E12">
+        <v>7.199999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>13.6</v>
+      </c>
+      <c r="C13">
+        <v>1.7</v>
+      </c>
+      <c r="D13">
+        <v>3.7</v>
+      </c>
+      <c r="E13">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
-        <v>1.4</v>
-      </c>
-      <c r="C13">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="D13">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B14">
-        <v>17.1</v>
+        <v>0.3</v>
       </c>
       <c r="C14">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="D14">
-        <v>0.8999999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>6.1</v>
+      </c>
+      <c r="E14">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D15">
         <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3021,28 +3118,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3053,25 +3150,25 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>93.29000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>116.73</v>
+        <v>117.01</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.576</v>
       </c>
       <c r="H2">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3079,28 +3176,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>77.89</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3">
-        <v>114.66</v>
+        <v>114.21</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3108,28 +3205,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>109.03</v>
+        <v>85.91</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>112.69</v>
+        <v>111.62</v>
       </c>
       <c r="G4">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3137,28 +3234,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>98.63</v>
+        <v>110.29</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5">
-        <v>115.18</v>
+        <v>109.93</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H5">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3166,28 +3263,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>103.42</v>
+        <v>100.59</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>114.01</v>
+        <v>110.05</v>
       </c>
       <c r="G6">
-        <v>0.542</v>
+        <v>0.455</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3195,28 +3292,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>108.6</v>
+        <v>111.29</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
       <c r="F7">
-        <v>110.73</v>
+        <v>111.2</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H7">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3224,28 +3321,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>108.43</v>
+        <v>115.98</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8">
-        <v>112.45</v>
+        <v>108.31</v>
       </c>
       <c r="G8">
-        <v>0.542</v>
+        <v>0.455</v>
       </c>
       <c r="H8">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3253,28 +3350,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>90.02</v>
+        <v>121.4</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>112.61</v>
+        <v>107.94</v>
       </c>
       <c r="G9">
-        <v>0.542</v>
+        <v>0.485</v>
       </c>
       <c r="H9">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3282,28 +3379,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>120.55</v>
+        <v>128.91</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>105.64</v>
+        <v>108.87</v>
       </c>
       <c r="G10">
-        <v>0.417</v>
+        <v>0.515</v>
       </c>
       <c r="H10">
-        <v>-1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3311,28 +3408,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>107.44</v>
+      </c>
+      <c r="G11">
+        <v>0.515</v>
+      </c>
+      <c r="H11">
+        <v>-1.7</v>
+      </c>
+      <c r="I11">
         <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11">
-        <v>135.92</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>107.88</v>
-      </c>
-      <c r="G11">
-        <v>0.5</v>
-      </c>
-      <c r="H11">
-        <v>-1.5</v>
-      </c>
-      <c r="I11">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3343,25 +3440,25 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>113.46</v>
+        <v>105.31</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>106.61</v>
+        <v>106.02</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H12">
-        <v>-2.2</v>
+        <v>-2.7</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3372,25 +3469,25 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>95.08</v>
+        <v>94.5</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>105.85</v>
+        <v>103.92</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H13">
-        <v>-2.8</v>
+        <v>-4</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3401,25 +3498,25 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D14">
-        <v>150.58</v>
+        <v>137.17</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
       </c>
       <c r="F14">
-        <v>104.82</v>
+        <v>105.38</v>
       </c>
       <c r="G14">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H14">
-        <v>-3</v>
+        <v>-4.4</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3430,25 +3527,25 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15">
-        <v>137.82</v>
+        <v>132.88</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>102.85</v>
+        <v>104.37</v>
       </c>
       <c r="G15">
-        <v>0.458</v>
+        <v>0.515</v>
       </c>
       <c r="H15">
-        <v>-3.2</v>
+        <v>-5</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3463,31 +3560,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3495,16 +3592,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>150.58</v>
+        <v>137.1666666666667</v>
       </c>
       <c r="E2">
-        <v>301.16</v>
+        <v>411.5</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -3513,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3524,16 +3621,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>137.82</v>
+        <v>132.88</v>
       </c>
       <c r="E3">
-        <v>275.64</v>
+        <v>398.64</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -3542,10 +3639,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3553,86 +3650,86 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>135.92</v>
+        <v>128.9066666666667</v>
       </c>
       <c r="E4">
-        <v>271.84</v>
+        <v>386.72</v>
       </c>
       <c r="F4">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>120.55</v>
+        <v>121.4</v>
       </c>
       <c r="E5">
-        <v>241.1</v>
+        <v>364.2</v>
       </c>
       <c r="F5">
-        <v>96.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>113.46</v>
+        <v>115.98</v>
       </c>
       <c r="E6">
-        <v>226.92</v>
+        <v>347.94</v>
       </c>
       <c r="F6">
-        <v>92.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3640,144 +3737,144 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>109.03</v>
+        <v>110.2866666666667</v>
       </c>
       <c r="E7">
-        <v>218.06</v>
+        <v>330.86</v>
       </c>
       <c r="F7">
-        <v>86.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>108.6</v>
+        <v>111.2933333333333</v>
       </c>
       <c r="E8">
-        <v>217.2</v>
+        <v>333.88</v>
       </c>
       <c r="F8">
-        <v>70.39999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D9">
+        <v>105.3133333333333</v>
+      </c>
+      <c r="E9">
+        <v>315.94</v>
+      </c>
+      <c r="F9">
+        <v>65.3</v>
+      </c>
+      <c r="G9">
         <v>0.5</v>
       </c>
-      <c r="D9">
-        <v>108.43</v>
-      </c>
-      <c r="E9">
-        <v>216.86</v>
-      </c>
-      <c r="F9">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="G9">
-        <v>0.3</v>
-      </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>98.63</v>
+        <v>100.5866666666667</v>
       </c>
       <c r="E10">
-        <v>197.26</v>
+        <v>301.76</v>
       </c>
       <c r="F10">
-        <v>42.3</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>103.42</v>
+        <v>93.93333333333334</v>
       </c>
       <c r="E11">
-        <v>206.84</v>
+        <v>281.8</v>
       </c>
       <c r="F11">
-        <v>33.7</v>
+        <v>9.1</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>9.4</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3785,86 +3882,86 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>95.08</v>
+        <v>94.5</v>
       </c>
       <c r="E12">
-        <v>190.16</v>
+        <v>283.5</v>
       </c>
       <c r="F12">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>10.3</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>93.28999999999999</v>
+        <v>96.48666666666666</v>
       </c>
       <c r="E13">
-        <v>186.58</v>
+        <v>289.46</v>
       </c>
       <c r="F13">
-        <v>2.5</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="G13">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D14">
-        <v>90.02</v>
+        <v>91.62666666666667</v>
       </c>
       <c r="E14">
-        <v>180.04</v>
+        <v>274.88</v>
       </c>
       <c r="F14">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="G14">
-        <v>11.7</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3872,28 +3969,28 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>77.89</v>
+        <v>85.91333333333334</v>
       </c>
       <c r="E15">
-        <v>155.78</v>
+        <v>257.74</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G15">
-        <v>82.39999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3908,19 +4005,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3931,16 +4028,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3951,10 +4048,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -3968,16 +4065,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>57</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>102</v>
@@ -3988,16 +4085,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>103</v>
@@ -4008,19 +4105,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4028,19 +4125,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4048,19 +4145,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4068,19 +4165,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4088,19 +4185,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4108,19 +4205,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4128,19 +4225,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D12">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4148,19 +4245,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4168,19 +4265,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4188,16 +4285,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>108</v>
@@ -4210,21 +4307,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4234,11 +4334,14 @@
       <c r="C2">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -4248,175 +4351,214 @@
       <c r="C3">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>-1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
         <v>-1</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="C9">
+        <v>-3</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-5</v>
+      </c>
+      <c r="C10">
+        <v>-9</v>
+      </c>
+      <c r="D10">
+        <v>-2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>-3</v>
+      </c>
+      <c r="C11">
+        <v>-1</v>
+      </c>
+      <c r="D11">
+        <v>-3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
         <v>2</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>-3</v>
-      </c>
-      <c r="C9">
-        <v>-1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>-1</v>
-      </c>
-      <c r="C10">
-        <v>-3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>-4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
       </c>
       <c r="C12">
         <v>-4</v>
       </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12">
+        <v>-3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>-4</v>
+      </c>
+      <c r="D13">
+        <v>-15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>-7</v>
+      </c>
+      <c r="C14">
+        <v>-13</v>
+      </c>
+      <c r="D14">
+        <v>-15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
+      <c r="B15">
         <v>-4</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>-9</v>
       </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14">
-        <v>-5</v>
-      </c>
-      <c r="C14">
-        <v>-9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15">
-        <v>-7</v>
-      </c>
-      <c r="C15">
-        <v>-13</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>-17</v>
+      </c>
+      <c r="E15" t="s">
         <v>108</v>
       </c>
     </row>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="126">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -67,16 +67,19 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -154,6 +157,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -178,45 +184,45 @@
     <t>nicholas spadaro</t>
   </si>
   <si>
+    <t>Kathy Dillon</t>
+  </si>
+  <si>
     <t>Brendan Fanning</t>
   </si>
   <si>
+    <t>Antonio  Spadaro</t>
+  </si>
+  <si>
     <t>Zachary Dillon</t>
   </si>
   <si>
-    <t>Kathy Dillon</t>
+    <t>Sal Spadaro</t>
   </si>
   <si>
     <t>gabriella spadaro</t>
   </si>
   <si>
-    <t>Sal Spadaro</t>
-  </si>
-  <si>
-    <t>Antonio  Spadaro</t>
+    <t>Marissa Rodriguez</t>
   </si>
   <si>
     <t>Michael Dillon</t>
   </si>
   <si>
-    <t>Marissa Rodriguez</t>
-  </si>
-  <si>
     <t>Mikaela Mitcho</t>
   </si>
   <si>
     <t>Ryan Lesiak</t>
   </si>
   <si>
+    <t>Lawrence Rosello</t>
+  </si>
+  <si>
     <t>Stephanie Mattei</t>
   </si>
   <si>
     <t>Josh Formola</t>
   </si>
   <si>
-    <t>Lawrence Rosello</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -241,64 +247,67 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>12.3-1.7-0.1</t>
-  </si>
-  <si>
-    <t>11.3-2.6-0.1</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
-  </si>
-  <si>
-    <t>9.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.1-0.2</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>10.5-3.3-0.1</t>
+  </si>
+  <si>
+    <t>11.2-2.7-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.2-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.6-0.2</t>
+  </si>
+  <si>
+    <t>5.6-8.3-0.1</t>
   </si>
   <si>
     <t>5.2-8.7-0.1</t>
   </si>
   <si>
-    <t>4.1-9.7-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.1-0.1</t>
-  </si>
-  <si>
-    <t>2.3-11.6-0.1</t>
-  </si>
-  <si>
-    <t>13-1</t>
+    <t>5.0-8.9-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
+  </si>
+  <si>
+    <t>3.3-10.5-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>11-3</t>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
@@ -307,6 +316,9 @@
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
@@ -316,7 +328,7 @@
     <t>4-10</t>
   </si>
   <si>
-    <t>2-12</t>
+    <t>3-11</t>
   </si>
   <si>
     <t>Owners</t>
@@ -328,28 +340,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↑9</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
-    <t>↓8</t>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -359,6 +377,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -798,16 +819,16 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
@@ -822,7 +843,7 @@
         <v>14</v>
       </c>
       <c r="M2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" t="s">
         <v>14</v>
@@ -836,46 +857,46 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -883,31 +904,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
         <v>14</v>
@@ -916,13 +937,13 @@
         <v>14</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N4" t="s">
         <v>14</v>
       </c>
       <c r="O4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -933,7 +954,7 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -942,7 +963,7 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -954,19 +975,19 @@
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O5" t="s">
         <v>17</v>
@@ -980,43 +1001,43 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" t="s">
         <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="s">
         <v>14</v>
       </c>
       <c r="O6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1024,46 +1045,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
         <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1071,46 +1092,46 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
       <c r="K8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1118,46 +1139,46 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" t="s">
-        <v>15</v>
-      </c>
-      <c r="N9" t="s">
-        <v>15</v>
-      </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1177,31 +1198,31 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10" t="s">
         <v>17</v>
@@ -1212,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -1224,10 +1245,10 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1236,22 +1257,22 @@
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1259,46 +1280,46 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1309,43 +1330,43 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s">
         <v>16</v>
       </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" t="s">
         <v>16</v>
       </c>
-      <c r="I13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" t="s">
-        <v>15</v>
-      </c>
-      <c r="N13" t="s">
-        <v>15</v>
-      </c>
       <c r="O13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1353,46 +1374,46 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L14" t="s">
         <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1400,46 +1421,46 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1449,30 +1470,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1480,25 +1501,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>-9</v>
       </c>
       <c r="F2">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1506,25 +1527,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F3">
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1532,25 +1553,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>-17</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1558,25 +1579,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>-15</v>
-      </c>
-      <c r="F5">
-        <v>-17</v>
-      </c>
       <c r="G5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1584,25 +1605,129 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>-9</v>
+      </c>
+      <c r="F6">
+        <v>-4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>-3</v>
+      </c>
+      <c r="G7">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="H7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>0</v>
+      <c r="H9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>-15</v>
+      </c>
+      <c r="F10">
+        <v>-17</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1617,13 +1742,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1634,7 +1759,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.4285714285714285</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -1645,13 +1770,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1659,13 +1784,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.142857142857143</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1673,10 +1798,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>1.214285714285714</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1687,10 +1812,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1.285714285714286</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -1701,13 +1826,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>1.357142857142857</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1715,10 +1840,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.428571428571429</v>
+        <v>1.928571428571429</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1729,10 +1854,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1743,10 +1868,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>1.857142857142857</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1757,13 +1882,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>1.857142857142857</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1771,13 +1896,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>1.857142857142857</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1785,10 +1910,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1.928571428571429</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -1802,10 +1927,10 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1816,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2.142857142857143</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -1834,16 +1959,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1851,16 +1976,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>2.642857142857143</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="D2">
-        <v>-0.3571428571428572</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1868,13 +1993,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -1888,13 +2013,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>2.357142857142857</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D4">
-        <v>-0.6428571428571428</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1902,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -1919,13 +2044,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1.857142857142857</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="D6">
-        <v>-0.1428571428571428</v>
+        <v>-0.6428571428571428</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -1939,13 +2064,13 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>1.785714285714286</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>-0.2142857142857142</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1953,16 +2078,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1.642857142857143</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D8">
-        <v>-0.3571428571428572</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1970,16 +2095,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.285714285714286</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D9">
-        <v>0.2857142857142858</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1987,16 +2112,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1.071428571428571</v>
+        <v>1.5</v>
       </c>
       <c r="D10">
-        <v>0.0714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2004,16 +2129,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>0.9285714285714286</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D11">
-        <v>0.9285714285714286</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2021,16 +2146,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>0.8571428571428571</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D12">
-        <v>0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2038,16 +2163,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>0.7857142857142857</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="D13">
-        <v>-0.2142857142857143</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2055,16 +2180,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0.7142857142857143</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D14">
-        <v>-1.285714285714286</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2072,13 +2197,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>0.5714285714285714</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D15">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -2096,52 +2221,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2149,31 +2274,31 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>64.90000000000001</v>
+        <v>29.1</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>34.5</v>
       </c>
       <c r="D2">
-        <v>10.3</v>
+        <v>20.1</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2191,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2199,22 +2324,22 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>56.7</v>
       </c>
       <c r="C3">
-        <v>43.5</v>
+        <v>28.4</v>
       </c>
       <c r="D3">
-        <v>27.9</v>
+        <v>8.9</v>
       </c>
       <c r="E3">
-        <v>8.699999999999999</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H3">
         <v>0.2</v>
@@ -2223,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2241,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2249,34 +2374,34 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>16</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C4">
-        <v>27.4</v>
+        <v>19.3</v>
       </c>
       <c r="D4">
-        <v>37.4</v>
+        <v>29.3</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>20.9</v>
       </c>
       <c r="F4">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="G4">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2291,49 +2416,49 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C5">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="D5">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>24.3</v>
       </c>
       <c r="F5">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L5">
+        <v>0.3</v>
+      </c>
+      <c r="M5">
         <v>0.2</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
       <c r="N5">
         <v>0</v>
       </c>
@@ -2341,212 +2466,212 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>99.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="C6">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="D6">
-        <v>8.300000000000001</v>
+        <v>15.7</v>
       </c>
       <c r="E6">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="F6">
-        <v>27.2</v>
+        <v>22.3</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>14.1</v>
       </c>
       <c r="H6">
-        <v>11.9</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K6">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L6">
+        <v>0.2</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>0.1</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
+        <v>1.4</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F7">
+        <v>14.6</v>
+      </c>
+      <c r="G7">
+        <v>23</v>
+      </c>
+      <c r="H7">
+        <v>18.2</v>
+      </c>
+      <c r="I7">
+        <v>10.9</v>
+      </c>
+      <c r="J7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K7">
+        <v>5.9</v>
+      </c>
+      <c r="L7">
+        <v>3.3</v>
+      </c>
+      <c r="M7">
+        <v>1.5</v>
+      </c>
+      <c r="N7">
         <v>0.5</v>
       </c>
-      <c r="D7">
-        <v>1.6</v>
-      </c>
-      <c r="E7">
-        <v>9.9</v>
-      </c>
-      <c r="F7">
-        <v>18.1</v>
-      </c>
-      <c r="G7">
-        <v>24.5</v>
-      </c>
-      <c r="H7">
-        <v>22.7</v>
-      </c>
-      <c r="I7">
-        <v>13.8</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>1.7</v>
-      </c>
-      <c r="L7">
-        <v>0.6</v>
-      </c>
-      <c r="M7">
-        <v>0.3</v>
-      </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.2</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
-        <v>91.2</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="E8">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="F8">
+        <v>9.4</v>
+      </c>
+      <c r="G8">
         <v>16.3</v>
       </c>
-      <c r="G8">
-        <v>23.6</v>
-      </c>
       <c r="H8">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="I8">
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
       <c r="J8">
-        <v>7.3</v>
+        <v>12.3</v>
       </c>
       <c r="K8">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="L8">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="M8">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="N8">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>88.8</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="F9">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="H9">
-        <v>17.8</v>
+        <v>14.7</v>
       </c>
       <c r="I9">
-        <v>28.6</v>
+        <v>18.7</v>
       </c>
       <c r="J9">
-        <v>19.1</v>
+        <v>15.1</v>
       </c>
       <c r="K9">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="M9">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="N9">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>65.3</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2555,43 +2680,43 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="H10">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="I10">
-        <v>16.9</v>
+        <v>11.4</v>
       </c>
       <c r="J10">
-        <v>23.2</v>
+        <v>13.3</v>
       </c>
       <c r="K10">
-        <v>19.4</v>
+        <v>17.2</v>
       </c>
       <c r="L10">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="M10">
-        <v>8.4</v>
+        <v>13.1</v>
       </c>
       <c r="N10">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O10">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2605,148 +2730,148 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="H11">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I11">
-        <v>5.6</v>
+        <v>10.6</v>
       </c>
       <c r="J11">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="K11">
-        <v>17.8</v>
+        <v>14.1</v>
       </c>
       <c r="L11">
-        <v>17.4</v>
+        <v>15.8</v>
       </c>
       <c r="M11">
-        <v>18.4</v>
+        <v>14.4</v>
       </c>
       <c r="N11">
-        <v>16.1</v>
+        <v>13.3</v>
       </c>
       <c r="O11">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P11">
-        <v>9.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
         <v>0.1</v>
       </c>
       <c r="E12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G12">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>11.2</v>
+        <v>13</v>
       </c>
       <c r="K12">
-        <v>16.5</v>
+        <v>14.7</v>
       </c>
       <c r="L12">
-        <v>17.4</v>
+        <v>14.8</v>
       </c>
       <c r="M12">
-        <v>18.3</v>
+        <v>13.7</v>
       </c>
       <c r="N12">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
       <c r="O12">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G13">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="I13">
-        <v>3.7</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="K13">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="L13">
-        <v>17.5</v>
+        <v>14.8</v>
       </c>
       <c r="M13">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="N13">
-        <v>20.7</v>
+        <v>16.8</v>
       </c>
       <c r="O13">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="P13">
-        <v>5.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2758,45 +2883,45 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G14">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="H14">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="I14">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J14">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K14">
-        <v>15.6</v>
+        <v>10.1</v>
       </c>
       <c r="L14">
-        <v>21.6</v>
+        <v>13.2</v>
       </c>
       <c r="M14">
-        <v>25</v>
+        <v>20.4</v>
       </c>
       <c r="N14">
-        <v>20.3</v>
+        <v>17.9</v>
       </c>
       <c r="O14">
-        <v>6.2</v>
+        <v>18.7</v>
       </c>
       <c r="P14">
-        <v>4.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2811,37 +2936,37 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H15">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="I15">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J15">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="K15">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="L15">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M15">
-        <v>9.4</v>
+        <v>14.1</v>
       </c>
       <c r="N15">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
       <c r="O15">
-        <v>60.2</v>
+        <v>41.5</v>
       </c>
       <c r="P15">
-        <v>0.3</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2851,24 +2976,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2884,8 +3012,11 @@
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2901,209 +3032,248 @@
       <c r="E3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>97.3</v>
+        <v>96.3</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E4">
+        <v>99.3</v>
+      </c>
+      <c r="F4">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="C5">
+        <v>38.9</v>
+      </c>
+      <c r="D5">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E5">
+        <v>97.2</v>
+      </c>
+      <c r="F5">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C5">
-        <v>67.7</v>
-      </c>
-      <c r="D5">
-        <v>98.7</v>
-      </c>
-      <c r="E5">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
+      <c r="C6">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>98.3</v>
+      </c>
+      <c r="E6">
+        <v>95.5</v>
+      </c>
+      <c r="F6">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>46.3</v>
-      </c>
-      <c r="C6">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="D6">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="E6">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="B7">
+        <v>44.8</v>
+      </c>
+      <c r="C7">
+        <v>98</v>
+      </c>
+      <c r="D7">
+        <v>98.8</v>
+      </c>
+      <c r="E7">
+        <v>81.10000000000001</v>
+      </c>
+      <c r="F7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>0.3</v>
+      </c>
+      <c r="C8">
+        <v>11.1</v>
+      </c>
+      <c r="D8">
+        <v>6.3</v>
+      </c>
+      <c r="E8">
+        <v>69.8</v>
+      </c>
+      <c r="F8">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>71.2</v>
-      </c>
-      <c r="C7">
-        <v>87.8</v>
-      </c>
-      <c r="D7">
-        <v>92.30000000000001</v>
-      </c>
-      <c r="E7">
-        <v>90.90000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>38</v>
-      </c>
-      <c r="D8">
-        <v>92.2</v>
-      </c>
-      <c r="E8">
-        <v>90.10000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B9">
-        <v>95.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C9">
-        <v>94.89999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D9">
-        <v>68.10000000000001</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="E9">
-        <v>68.30000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>58.7</v>
+      </c>
+      <c r="F9">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>70.5</v>
+        <v>0.6</v>
       </c>
       <c r="C10">
-        <v>69.59999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="D10">
-        <v>23.6</v>
+        <v>6.2</v>
       </c>
       <c r="E10">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="D11">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>23.7</v>
+      </c>
+      <c r="F11">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>0.7000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>8.6</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
-        <v>6.3</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
-        <v>7.199999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>16.4</v>
+      </c>
+      <c r="F12">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="C13">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D13">
+        <v>69</v>
+      </c>
+      <c r="E13">
+        <v>17.2</v>
+      </c>
+      <c r="F13">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>74.3</v>
+      </c>
+      <c r="C14">
+        <v>69.8</v>
+      </c>
+      <c r="D14">
+        <v>23.2</v>
+      </c>
+      <c r="E14">
+        <v>7.5</v>
+      </c>
+      <c r="F14">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <v>13.6</v>
-      </c>
-      <c r="C13">
-        <v>1.7</v>
-      </c>
-      <c r="D13">
-        <v>3.7</v>
-      </c>
-      <c r="E13">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14">
-        <v>0.3</v>
-      </c>
-      <c r="C14">
-        <v>7.7</v>
-      </c>
-      <c r="D14">
-        <v>6.1</v>
-      </c>
-      <c r="E14">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B15">
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="C15">
-        <v>0.1</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="E15">
-        <v>0.1</v>
+        <v>4.6</v>
+      </c>
+      <c r="F15">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3118,28 +3288,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3150,25 +3320,25 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>91.63</v>
+        <v>96.94</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>117.01</v>
+        <v>114.91</v>
       </c>
       <c r="G2">
-        <v>0.576</v>
+        <v>0.55</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3176,28 +3346,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>93.93000000000001</v>
+        <v>105.27</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>114.21</v>
+        <v>110.89</v>
       </c>
       <c r="G3">
-        <v>0.515</v>
+        <v>0.45</v>
       </c>
       <c r="H3">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3205,28 +3375,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>85.91</v>
+        <v>96.3</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>111.62</v>
+        <v>111.51</v>
       </c>
       <c r="G4">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H4">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3234,28 +3404,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>110.29</v>
+        <v>109.33</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>109.93</v>
+        <v>108.68</v>
       </c>
       <c r="G5">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H5">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3263,28 +3433,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>100.59</v>
+        <v>98.59</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>110.05</v>
+        <v>107.59</v>
       </c>
       <c r="G6">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="H6">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3295,25 +3465,25 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>111.29</v>
+        <v>115.13</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
       <c r="F7">
-        <v>111.2</v>
+        <v>108.49</v>
       </c>
       <c r="G7">
-        <v>0.545</v>
+        <v>0.475</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3321,28 +3491,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>115.98</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>108.31</v>
+        <v>107.2</v>
       </c>
       <c r="G8">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H8">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3350,28 +3520,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>121.4</v>
+        <v>122.06</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9">
-        <v>107.94</v>
+        <v>109.28</v>
       </c>
       <c r="G9">
-        <v>0.485</v>
+        <v>0.575</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3379,28 +3549,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>128.91</v>
+        <v>114.07</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>108.87</v>
+        <v>107.88</v>
       </c>
       <c r="G10">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3411,25 +3581,25 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11">
-        <v>96.48999999999999</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>107.44</v>
+        <v>107.82</v>
       </c>
       <c r="G11">
-        <v>0.515</v>
+        <v>0.55</v>
       </c>
       <c r="H11">
-        <v>-1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3440,25 +3610,25 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12">
-        <v>105.31</v>
+        <v>96.58</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>106.02</v>
+        <v>105.75</v>
       </c>
       <c r="G12">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H12">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3466,28 +3636,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13">
-        <v>94.5</v>
+        <v>129.99</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>103.92</v>
+        <v>105.15</v>
       </c>
       <c r="G13">
-        <v>0.455</v>
+        <v>0.55</v>
       </c>
       <c r="H13">
-        <v>-4</v>
+        <v>-4.8</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3495,28 +3665,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14">
-        <v>137.17</v>
+        <v>108.58</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F14">
-        <v>105.38</v>
+        <v>103.27</v>
       </c>
       <c r="G14">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H14">
-        <v>-4.4</v>
+        <v>-5.8</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3524,28 +3694,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15">
-        <v>132.88</v>
+        <v>126.54</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>104.37</v>
+        <v>103.07</v>
       </c>
       <c r="G15">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H15">
-        <v>-5</v>
+        <v>-6.4</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3560,31 +3730,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3592,28 +3762,28 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D2">
-        <v>137.1666666666667</v>
+        <v>126.54</v>
       </c>
       <c r="E2">
-        <v>411.5</v>
+        <v>506.16</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3621,28 +3791,28 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>132.88</v>
+        <v>129.99</v>
       </c>
       <c r="E3">
-        <v>398.64</v>
+        <v>519.96</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3650,202 +3820,202 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>128.9066666666667</v>
+        <v>122.06</v>
       </c>
       <c r="E4">
-        <v>386.72</v>
+        <v>488.24</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
-        <v>121.4</v>
+        <v>115.13</v>
       </c>
       <c r="E5">
-        <v>364.2</v>
+        <v>460.52</v>
       </c>
       <c r="F5">
-        <v>99.09999999999999</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D6">
-        <v>115.98</v>
+        <v>114.075</v>
       </c>
       <c r="E6">
-        <v>347.94</v>
+        <v>456.3</v>
       </c>
       <c r="F6">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>110.2866666666667</v>
+        <v>109.325</v>
       </c>
       <c r="E7">
-        <v>330.86</v>
+        <v>437.3</v>
       </c>
       <c r="F7">
-        <v>91.2</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>111.2933333333333</v>
+        <v>108.58</v>
       </c>
       <c r="E8">
-        <v>333.88</v>
+        <v>434.32</v>
       </c>
       <c r="F8">
-        <v>88.8</v>
+        <v>68.8</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>105.3133333333333</v>
+        <v>105.265</v>
       </c>
       <c r="E9">
-        <v>315.94</v>
+        <v>421.06</v>
       </c>
       <c r="F9">
-        <v>65.3</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D10">
-        <v>100.5866666666667</v>
+        <v>96.935</v>
       </c>
       <c r="E10">
-        <v>301.76</v>
+        <v>387.74</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3853,144 +4023,144 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>93.93333333333334</v>
+        <v>96.30000000000001</v>
       </c>
       <c r="E11">
-        <v>281.8</v>
+        <v>385.2</v>
       </c>
       <c r="F11">
-        <v>9.1</v>
+        <v>22.3</v>
       </c>
       <c r="G11">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D12">
-        <v>94.5</v>
+        <v>98.595</v>
       </c>
       <c r="E12">
-        <v>283.5</v>
+        <v>394.38</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>19.9</v>
       </c>
       <c r="G12">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D13">
-        <v>96.48666666666666</v>
+        <v>96.58</v>
       </c>
       <c r="E13">
-        <v>289.46</v>
+        <v>386.32</v>
       </c>
       <c r="F13">
-        <v>5.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="G13">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C14">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="D14">
-        <v>91.62666666666667</v>
+        <v>95.25999999999999</v>
       </c>
       <c r="E14">
-        <v>274.88</v>
+        <v>381.04</v>
       </c>
       <c r="F14">
-        <v>4.9</v>
+        <v>9.9</v>
       </c>
       <c r="G14">
-        <v>6.2</v>
+        <v>18.7</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>85.91333333333334</v>
+        <v>96.85499999999999</v>
       </c>
       <c r="E15">
-        <v>257.74</v>
+        <v>387.42</v>
       </c>
       <c r="F15">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>60.2</v>
+        <v>41.5</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4005,19 +4175,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4031,13 +4201,13 @@
         <v>63</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4048,16 +4218,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4065,19 +4235,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4088,16 +4258,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4105,19 +4275,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4125,10 +4295,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -4137,7 +4307,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4145,19 +4315,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4165,19 +4335,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4191,10 +4361,10 @@
         <v>53</v>
       </c>
       <c r="D10">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
         <v>105</v>
@@ -4208,16 +4378,16 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D11">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4225,19 +4395,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D12">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4245,16 +4415,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
         <v>107</v>
@@ -4265,19 +4435,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4288,7 +4458,7 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15">
         <v>-17</v>
@@ -4297,7 +4467,7 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -4307,24 +4477,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>118</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4337,11 +4510,14 @@
       <c r="D2">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -4354,28 +4530,34 @@
       <c r="D3">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4388,79 +4570,94 @@
       <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6">
+        <v>-3</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="F6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>-4</v>
+      </c>
+      <c r="D8">
+        <v>-3</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>-1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
+      <c r="F8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="B9">
         <v>-1</v>
       </c>
       <c r="C9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>-2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -4473,11 +4670,14 @@
       <c r="D10">
         <v>-2</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10">
+        <v>-3</v>
+      </c>
+      <c r="F10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -4490,62 +4690,74 @@
       <c r="D11">
         <v>-3</v>
       </c>
-      <c r="E11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11">
+        <v>-6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>2</v>
       </c>
-      <c r="C12">
-        <v>-4</v>
-      </c>
-      <c r="D12">
-        <v>-3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12">
+        <v>-7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="C13">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="D13">
         <v>-15</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13">
+        <v>-9</v>
+      </c>
+      <c r="F13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="D14">
         <v>-15</v>
       </c>
-      <c r="E14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="E14">
+        <v>-16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -4558,8 +4770,11 @@
       <c r="D15">
         <v>-17</v>
       </c>
-      <c r="E15" t="s">
-        <v>108</v>
+      <c r="E15">
+        <v>-17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="123">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -67,19 +67,22 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -160,6 +163,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -196,13 +202,16 @@
     <t>Zachary Dillon</t>
   </si>
   <si>
+    <t>Marissa Rodriguez</t>
+  </si>
+  <si>
+    <t>gabriella spadaro</t>
+  </si>
+  <si>
     <t>Sal Spadaro</t>
   </si>
   <si>
-    <t>gabriella spadaro</t>
-  </si>
-  <si>
-    <t>Marissa Rodriguez</t>
+    <t>Ryan Lesiak</t>
   </si>
   <si>
     <t>Michael Dillon</t>
@@ -211,9 +220,6 @@
     <t>Mikaela Mitcho</t>
   </si>
   <si>
-    <t>Ryan Lesiak</t>
-  </si>
-  <si>
     <t>Lawrence Rosello</t>
   </si>
   <si>
@@ -247,58 +253,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>10.5-3.3-0.1</t>
-  </si>
-  <si>
-    <t>11.2-2.7-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.2-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.2-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.6-0.2</t>
-  </si>
-  <si>
-    <t>5.6-8.3-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>3.3-10.5-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>10.8-3.1-0.1</t>
+  </si>
+  <si>
+    <t>11.3-2.7-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.8-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9-0.1</t>
+  </si>
+  <si>
+    <t>3.3-10.6-0.1</t>
+  </si>
+  <si>
+    <t>3.0-10.9-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -307,9 +310,6 @@
     <t>12-2</t>
   </si>
   <si>
-    <t>10-4</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
@@ -322,9 +322,6 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
@@ -340,34 +337,25 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓7</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓5</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -380,6 +368,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -834,7 +825,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
         <v>14</v>
@@ -860,43 +851,43 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L3" t="s">
         <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -913,7 +904,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
@@ -922,16 +913,16 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -940,7 +931,7 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O4" t="s">
         <v>15</v>
@@ -951,46 +942,46 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1007,10 +998,10 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -1022,10 +1013,10 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L6" t="s">
         <v>17</v>
@@ -1048,43 +1039,43 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
       <c r="K7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M7" t="s">
-        <v>14</v>
-      </c>
       <c r="N7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1095,43 +1086,43 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s">
+      <c r="I8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
       <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" t="s">
         <v>16</v>
       </c>
-      <c r="K8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" t="s">
-        <v>14</v>
-      </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1148,25 +1139,25 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
         <v>17</v>
@@ -1175,7 +1166,7 @@
         <v>14</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
         <v>17</v>
@@ -1189,31 +1180,31 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -1222,10 +1213,10 @@
         <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1236,43 +1227,43 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" t="s">
         <v>17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1289,7 +1280,7 @@
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
@@ -1298,13 +1289,13 @@
         <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
         <v>14</v>
@@ -1336,7 +1327,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1345,16 +1336,16 @@
         <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1377,43 +1368,43 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L14" t="s">
         <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1424,13 +1415,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
@@ -1439,7 +1430,7 @@
         <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -1475,25 +1466,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1501,25 +1492,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>-9</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1530,22 +1521,22 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="F3">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1582,22 +1573,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>-16</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1605,25 +1596,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>-9</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1631,25 +1622,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="F7">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1660,22 +1651,22 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>-9</v>
+      </c>
+      <c r="F8">
+        <v>-4</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
       <c r="H8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1683,22 +1674,22 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>-3</v>
+      </c>
+      <c r="G9">
         <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
       </c>
       <c r="H9" t="s">
         <v>0</v>
@@ -1709,25 +1700,25 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10">
-        <v>-15</v>
-      </c>
-      <c r="F10">
-        <v>-17</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
       <c r="H10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1742,13 +1733,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1756,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0.9285714285714286</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1770,13 +1761,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1.285714285714286</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1784,13 +1775,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>1.642857142857143</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1801,7 +1792,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>1.642857142857143</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1812,13 +1803,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1.857142857142857</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1826,13 +1817,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>1.857142857142857</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1840,13 +1831,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>1.928571428571429</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1854,10 +1845,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1871,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>2.214285714285714</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1882,13 +1873,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>2.285714285714286</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1896,13 +1887,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>2.285714285714286</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1910,13 +1901,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>2.428571428571428</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1927,10 +1918,10 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>2.785714285714286</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1941,10 +1932,10 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2.857142857142857</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1959,16 +1950,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1979,13 +1970,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>3.285714285714286</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="D2">
-        <v>0.2857142857142856</v>
+        <v>0.1428571428571432</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1996,13 +1987,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>3.714285714285714</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2013,10 +2004,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>2.857142857142857</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="D4">
-        <v>-0.1428571428571428</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -2027,16 +2018,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>2.714285714285714</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D5">
-        <v>-0.2857142857142856</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2044,13 +2035,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2.357142857142857</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="D6">
-        <v>-0.6428571428571428</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -2061,16 +2052,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2078,16 +2069,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.857142857142857</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D8">
-        <v>0.8571428571428572</v>
+        <v>-0.4285714285714284</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2095,13 +2086,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>1.785714285714286</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D9">
-        <v>-0.2142857142857142</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -2112,16 +2103,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>-1.642857142857143</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2129,13 +2120,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>1.428571428571429</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D11">
-        <v>-1.571428571428571</v>
+        <v>-0.9285714285714284</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -2146,13 +2137,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>1.428571428571429</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D12">
-        <v>-0.5714285714285714</v>
+        <v>0.07142857142857162</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2166,13 +2157,13 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>1.357142857142857</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D13">
-        <v>1.357142857142857</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2183,10 +2174,10 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>1.285714285714286</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D14">
-        <v>0.2857142857142858</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -2221,52 +2212,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2274,31 +2265,31 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>29.1</v>
+        <v>31.3</v>
       </c>
       <c r="C2">
-        <v>34.5</v>
+        <v>53.6</v>
       </c>
       <c r="D2">
-        <v>20.1</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>9.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="G2">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="H2">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2316,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2324,31 +2315,31 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>56.7</v>
+        <v>65.3</v>
       </c>
       <c r="C3">
-        <v>28.4</v>
+        <v>25.4</v>
       </c>
       <c r="D3">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="G3">
+        <v>0.2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>0.4</v>
       </c>
-      <c r="H3">
-        <v>0.2</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2366,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2374,90 +2365,90 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>9.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>19.3</v>
+        <v>6.3</v>
       </c>
       <c r="D4">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="E4">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>10.5</v>
+        <v>15.3</v>
       </c>
       <c r="G4">
-        <v>6.3</v>
+        <v>11.8</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J4">
+        <v>2.8</v>
+      </c>
+      <c r="K4">
+        <v>2.2</v>
+      </c>
+      <c r="L4">
         <v>0.6</v>
       </c>
-      <c r="K4">
-        <v>0.2</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>99.2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="C5">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="D5">
-        <v>18.9</v>
+        <v>15.8</v>
       </c>
       <c r="E5">
-        <v>24.3</v>
+        <v>17.4</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>18.2</v>
       </c>
       <c r="G5">
-        <v>9.4</v>
+        <v>13.9</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="I5">
+        <v>7.5</v>
+      </c>
+      <c r="J5">
+        <v>4.7</v>
+      </c>
+      <c r="K5">
         <v>3.2</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>1.3</v>
       </c>
-      <c r="K5">
-        <v>0.3</v>
-      </c>
-      <c r="L5">
-        <v>0.3</v>
-      </c>
       <c r="M5">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2466,262 +2457,262 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>97.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="D6">
-        <v>15.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6">
-        <v>22.4</v>
+        <v>16.1</v>
       </c>
       <c r="F6">
-        <v>22.3</v>
+        <v>16.4</v>
       </c>
       <c r="G6">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
+        <v>2.7</v>
+      </c>
+      <c r="M6">
+        <v>0.9</v>
+      </c>
+      <c r="N6">
         <v>0.2</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
       </c>
       <c r="O6">
         <v>0.1</v>
       </c>
       <c r="P6">
-        <v>96.8</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>13.3</v>
       </c>
       <c r="E7">
-        <v>8.699999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="F7">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>13.9</v>
       </c>
       <c r="H7">
-        <v>18.2</v>
+        <v>13.5</v>
       </c>
       <c r="I7">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="J7">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="K7">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="M7">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N7">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>79.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D8">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="E8">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="G8">
-        <v>16.3</v>
+        <v>13.9</v>
       </c>
       <c r="H8">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="I8">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="J8">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="K8">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="L8">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="P8">
-        <v>68.8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="E9">
-        <v>2.8</v>
+        <v>8.5</v>
       </c>
       <c r="F9">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G9">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H9">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="I9">
-        <v>18.7</v>
+        <v>13.4</v>
       </c>
       <c r="J9">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="K9">
-        <v>10.8</v>
+        <v>8.9</v>
       </c>
       <c r="L9">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="M9">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>56.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="E10">
+        <v>3.6</v>
+      </c>
+      <c r="F10">
+        <v>7.4</v>
+      </c>
+      <c r="G10">
+        <v>8.6</v>
+      </c>
+      <c r="H10">
+        <v>12.3</v>
+      </c>
+      <c r="I10">
+        <v>14.8</v>
+      </c>
+      <c r="J10">
+        <v>16.5</v>
+      </c>
+      <c r="K10">
+        <v>15.9</v>
+      </c>
+      <c r="L10">
+        <v>13</v>
+      </c>
+      <c r="M10">
+        <v>4.7</v>
+      </c>
+      <c r="N10">
+        <v>1.3</v>
+      </c>
+      <c r="O10">
         <v>0.4</v>
       </c>
-      <c r="F10">
-        <v>2.5</v>
-      </c>
-      <c r="G10">
-        <v>5.1</v>
-      </c>
-      <c r="H10">
-        <v>8.4</v>
-      </c>
-      <c r="I10">
-        <v>11.4</v>
-      </c>
-      <c r="J10">
-        <v>13.3</v>
-      </c>
-      <c r="K10">
-        <v>17.2</v>
-      </c>
-      <c r="L10">
-        <v>16.3</v>
-      </c>
-      <c r="M10">
-        <v>13.1</v>
-      </c>
-      <c r="N10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O10">
-        <v>3.3</v>
-      </c>
       <c r="P10">
-        <v>28</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2730,43 +2721,43 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>0.7</v>
+      </c>
+      <c r="E11">
+        <v>1.9</v>
+      </c>
+      <c r="F11">
+        <v>2.2</v>
+      </c>
+      <c r="G11">
+        <v>4.5</v>
+      </c>
+      <c r="H11">
+        <v>7.7</v>
+      </c>
+      <c r="I11">
+        <v>12.2</v>
+      </c>
+      <c r="J11">
+        <v>17.3</v>
+      </c>
+      <c r="K11">
+        <v>22.2</v>
+      </c>
+      <c r="L11">
+        <v>20</v>
+      </c>
+      <c r="M11">
+        <v>7.9</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11">
         <v>0.4</v>
       </c>
-      <c r="E11">
-        <v>0.5</v>
-      </c>
-      <c r="F11">
-        <v>1.6</v>
-      </c>
-      <c r="G11">
-        <v>3.6</v>
-      </c>
-      <c r="H11">
-        <v>5.6</v>
-      </c>
-      <c r="I11">
-        <v>10.6</v>
-      </c>
-      <c r="J11">
-        <v>10.3</v>
-      </c>
-      <c r="K11">
-        <v>14.1</v>
-      </c>
-      <c r="L11">
-        <v>15.8</v>
-      </c>
-      <c r="M11">
-        <v>14.4</v>
-      </c>
-      <c r="N11">
-        <v>13.3</v>
-      </c>
-      <c r="O11">
-        <v>9.800000000000001</v>
-      </c>
       <c r="P11">
-        <v>22.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2777,46 +2768,46 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="F12">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="G12">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I12">
         <v>8.6</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="K12">
-        <v>14.7</v>
+        <v>20.1</v>
       </c>
       <c r="L12">
-        <v>14.8</v>
+        <v>20.2</v>
       </c>
       <c r="M12">
-        <v>13.7</v>
+        <v>11.8</v>
       </c>
       <c r="N12">
-        <v>13.9</v>
+        <v>5.4</v>
       </c>
       <c r="O12">
-        <v>10</v>
+        <v>0.9</v>
       </c>
       <c r="P12">
-        <v>19.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2827,46 +2818,46 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="H13">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="I13">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J13">
-        <v>9.9</v>
+        <v>2.5</v>
       </c>
       <c r="K13">
-        <v>13.7</v>
+        <v>6.5</v>
       </c>
       <c r="L13">
-        <v>14.8</v>
+        <v>12.1</v>
       </c>
       <c r="M13">
-        <v>12.6</v>
+        <v>33.4</v>
       </c>
       <c r="N13">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="O13">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="P13">
-        <v>18</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2883,40 +2874,40 @@
         <v>0</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>0.1</v>
       </c>
-      <c r="F14">
-        <v>0.3</v>
-      </c>
       <c r="G14">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="H14">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14">
-        <v>9.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>10.1</v>
+        <v>1.8</v>
       </c>
       <c r="L14">
-        <v>13.2</v>
+        <v>6.8</v>
       </c>
       <c r="M14">
-        <v>20.4</v>
+        <v>18.2</v>
       </c>
       <c r="N14">
-        <v>17.9</v>
+        <v>30.1</v>
       </c>
       <c r="O14">
-        <v>18.7</v>
+        <v>41.2</v>
       </c>
       <c r="P14">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2936,37 +2927,37 @@
         <v>0</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>0.1</v>
       </c>
-      <c r="G15">
-        <v>0.5</v>
-      </c>
       <c r="H15">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="I15">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J15">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="K15">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="L15">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="M15">
-        <v>14.1</v>
+        <v>18.7</v>
       </c>
       <c r="N15">
-        <v>23.3</v>
+        <v>32.1</v>
       </c>
       <c r="O15">
-        <v>41.5</v>
+        <v>40.6</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2976,27 +2967,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3010,13 +3004,16 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3035,245 +3032,284 @@
       <c r="F3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E4">
         <v>99.3</v>
       </c>
       <c r="F4">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>93.30000000000001</v>
+      </c>
+      <c r="G4">
+        <v>91.60000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>5.800000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="C5">
-        <v>38.9</v>
+        <v>98.7</v>
       </c>
       <c r="D5">
-        <v>91.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>97.2</v>
+        <v>81.2</v>
       </c>
       <c r="F5">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>89</v>
+      </c>
+      <c r="G5">
+        <v>89.60000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.3</v>
+      </c>
+      <c r="C6">
+        <v>9.4</v>
+      </c>
+      <c r="D6">
+        <v>7.1</v>
+      </c>
+      <c r="E6">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F6">
+        <v>86.2</v>
+      </c>
+      <c r="G6">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>65</v>
-      </c>
-      <c r="D6">
-        <v>98.3</v>
-      </c>
-      <c r="E6">
-        <v>95.5</v>
-      </c>
-      <c r="F6">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B7">
-        <v>44.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C7">
-        <v>98</v>
+        <v>66.10000000000001</v>
       </c>
       <c r="D7">
-        <v>98.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E7">
-        <v>81.10000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F7">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>78.7</v>
+      </c>
+      <c r="G7">
+        <v>85.59999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0.3</v>
       </c>
       <c r="C8">
-        <v>11.1</v>
+        <v>7.5</v>
       </c>
       <c r="D8">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="E8">
-        <v>69.8</v>
+        <v>26.9</v>
       </c>
       <c r="F8">
-        <v>68.40000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G8">
+        <v>68.60000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>4.8</v>
+      </c>
+      <c r="C9">
+        <v>39</v>
+      </c>
+      <c r="D9">
+        <v>91.7</v>
+      </c>
+      <c r="E9">
+        <v>96.8</v>
+      </c>
+      <c r="F9">
+        <v>66.60000000000001</v>
+      </c>
+      <c r="G9">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>99.2</v>
+      </c>
+      <c r="C10">
+        <v>24.5</v>
+      </c>
+      <c r="D10">
+        <v>9.4</v>
+      </c>
+      <c r="E10">
+        <v>19.7</v>
+      </c>
+      <c r="F10">
+        <v>43.2</v>
+      </c>
+      <c r="G10">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="C9">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="D9">
-        <v>91.60000000000001</v>
-      </c>
-      <c r="E9">
-        <v>58.7</v>
-      </c>
-      <c r="F9">
-        <v>55.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0.6</v>
-      </c>
-      <c r="C10">
-        <v>8.9</v>
-      </c>
-      <c r="D10">
-        <v>6.2</v>
-      </c>
-      <c r="E10">
-        <v>29</v>
-      </c>
-      <c r="F10">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="B11">
-        <v>99.2</v>
+        <v>75.5</v>
       </c>
       <c r="C11">
-        <v>23.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D11">
-        <v>9.800000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="E11">
-        <v>23.7</v>
+        <v>61.9</v>
       </c>
       <c r="F11">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>28.4</v>
+      </c>
+      <c r="G11">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E12">
-        <v>16.4</v>
+        <v>18.8</v>
       </c>
       <c r="F12">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>34.1</v>
+      </c>
+      <c r="G12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>92.90000000000001</v>
+        <v>94.69999999999999</v>
       </c>
       <c r="C13">
-        <v>94.59999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="D13">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E13">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="F13">
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>3.8</v>
+      </c>
+      <c r="G13">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>11.6</v>
+      </c>
+      <c r="C14">
+        <v>1.5</v>
+      </c>
+      <c r="D14">
+        <v>4.9</v>
+      </c>
+      <c r="E14">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="F14">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="G14">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>74.3</v>
-      </c>
-      <c r="C14">
-        <v>69.8</v>
-      </c>
-      <c r="D14">
-        <v>23.2</v>
-      </c>
-      <c r="E14">
-        <v>7.5</v>
-      </c>
-      <c r="F14">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B15">
-        <v>13.7</v>
+        <v>71.7</v>
       </c>
       <c r="C15">
+        <v>70</v>
+      </c>
+      <c r="D15">
+        <v>23.3</v>
+      </c>
+      <c r="E15">
+        <v>7.1</v>
+      </c>
+      <c r="F15">
         <v>0.8999999999999999</v>
       </c>
-      <c r="D15">
-        <v>4.7</v>
-      </c>
-      <c r="E15">
-        <v>4.6</v>
-      </c>
-      <c r="F15">
-        <v>3.1</v>
+      <c r="G15">
+        <v>0.8999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3288,28 +3324,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3320,25 +3356,25 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>96.94</v>
+        <v>107.14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>114.91</v>
+        <v>117.82</v>
       </c>
       <c r="G2">
-        <v>0.55</v>
+        <v>0.578</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3349,25 +3385,25 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>105.27</v>
+        <v>106.15</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>110.89</v>
+        <v>111.28</v>
       </c>
       <c r="G3">
-        <v>0.45</v>
+        <v>0.444</v>
       </c>
       <c r="H3">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3378,25 +3414,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>96.3</v>
+        <v>103.13</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>111.51</v>
+        <v>111.38</v>
       </c>
       <c r="G4">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3407,25 +3443,25 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>109.33</v>
+        <v>114.68</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>108.68</v>
+        <v>110.33</v>
       </c>
       <c r="G5">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H5">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3436,25 +3472,25 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>98.59</v>
+        <v>103.38</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>107.59</v>
+        <v>109.82</v>
       </c>
       <c r="G6">
-        <v>0.45</v>
+        <v>0.467</v>
       </c>
       <c r="H6">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3462,28 +3498,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>115.13</v>
+        <v>117.78</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
       <c r="F7">
-        <v>108.49</v>
+        <v>110.36</v>
       </c>
       <c r="G7">
-        <v>0.475</v>
+        <v>0.533</v>
       </c>
       <c r="H7">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3494,25 +3530,25 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>95.26000000000001</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
       <c r="F8">
-        <v>107.2</v>
+        <v>108.72</v>
       </c>
       <c r="G8">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3520,28 +3556,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9">
-        <v>122.06</v>
+        <v>107.6</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9">
-        <v>109.28</v>
+        <v>109.39</v>
       </c>
       <c r="G9">
-        <v>0.575</v>
+        <v>0.489</v>
       </c>
       <c r="H9">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3549,28 +3585,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>114.07</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>107.88</v>
+        <v>109.2</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H10">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3578,28 +3614,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11">
-        <v>96.84999999999999</v>
+        <v>112.44</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>107.82</v>
+        <v>108.23</v>
       </c>
       <c r="G11">
-        <v>0.55</v>
+        <v>0.511</v>
       </c>
       <c r="H11">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3607,28 +3643,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>96.58</v>
+        <v>95.8</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>105.75</v>
+        <v>107.01</v>
       </c>
       <c r="G12">
-        <v>0.475</v>
+        <v>0.533</v>
       </c>
       <c r="H12">
-        <v>-2.5</v>
+        <v>-4.8</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3639,25 +3675,25 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>129.99</v>
+        <v>133.2</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>105.15</v>
+        <v>108.83</v>
       </c>
       <c r="G13">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H13">
-        <v>-4.8</v>
+        <v>-5.1</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3668,25 +3704,25 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14">
-        <v>108.58</v>
+        <v>117.63</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>103.27</v>
+        <v>104.1</v>
       </c>
       <c r="G14">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H14">
-        <v>-5.8</v>
+        <v>-7.1</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3697,25 +3733,25 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15">
-        <v>126.54</v>
+        <v>128.08</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>103.07</v>
+        <v>104.35</v>
       </c>
       <c r="G15">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H15">
-        <v>-6.4</v>
+        <v>-7.9</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3730,31 +3766,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3762,28 +3798,28 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>126.54</v>
+        <v>128.084</v>
       </c>
       <c r="E2">
-        <v>506.16</v>
+        <v>640.42</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3791,28 +3827,28 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>129.99</v>
+        <v>133.2</v>
       </c>
       <c r="E3">
-        <v>519.96</v>
+        <v>666</v>
       </c>
       <c r="F3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3820,112 +3856,112 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>122.06</v>
+        <v>117.784</v>
       </c>
       <c r="E4">
-        <v>488.24</v>
+        <v>588.9200000000001</v>
       </c>
       <c r="F4">
-        <v>99.2</v>
+        <v>94</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>115.13</v>
+        <v>114.684</v>
       </c>
       <c r="E5">
-        <v>460.52</v>
+        <v>573.4200000000001</v>
       </c>
       <c r="F5">
-        <v>97.89999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C6">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D6">
-        <v>114.075</v>
+        <v>117.628</v>
       </c>
       <c r="E6">
-        <v>456.3</v>
+        <v>588.14</v>
       </c>
       <c r="F6">
-        <v>96.8</v>
+        <v>86.5</v>
       </c>
       <c r="G6">
         <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>109.325</v>
+        <v>112.436</v>
       </c>
       <c r="E7">
-        <v>437.3</v>
+        <v>562.1799999999999</v>
       </c>
       <c r="F7">
-        <v>79.80000000000001</v>
+        <v>84</v>
       </c>
       <c r="G7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
         <v>96</v>
@@ -3933,28 +3969,28 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D8">
-        <v>108.58</v>
+        <v>107.604</v>
       </c>
       <c r="E8">
-        <v>434.32</v>
+        <v>538.02</v>
       </c>
       <c r="F8">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="G8">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
         <v>97</v>
@@ -3962,89 +3998,89 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D9">
-        <v>105.265</v>
+        <v>107.14</v>
       </c>
       <c r="E9">
-        <v>421.06</v>
+        <v>535.7</v>
       </c>
       <c r="F9">
-        <v>56.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>96.935</v>
+        <v>103.132</v>
       </c>
       <c r="E10">
-        <v>387.74</v>
+        <v>515.6600000000001</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>48.2</v>
       </c>
       <c r="G10">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>96.30000000000001</v>
+        <v>106.148</v>
       </c>
       <c r="E11">
-        <v>385.2</v>
+        <v>530.74</v>
       </c>
       <c r="F11">
-        <v>22.3</v>
+        <v>29.2</v>
       </c>
       <c r="G11">
-        <v>9.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4052,28 +4088,28 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D12">
-        <v>98.595</v>
+        <v>103.384</v>
       </c>
       <c r="E12">
-        <v>394.38</v>
+        <v>516.92</v>
       </c>
       <c r="F12">
-        <v>19.9</v>
+        <v>26.5</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4081,25 +4117,25 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C13">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>96.58</v>
+        <v>95.244</v>
       </c>
       <c r="E13">
-        <v>386.32</v>
+        <v>476.22</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>2.4</v>
       </c>
       <c r="G13">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
         <v>99</v>
@@ -4110,25 +4146,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C14">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D14">
-        <v>95.25999999999999</v>
+        <v>88.544</v>
       </c>
       <c r="E14">
-        <v>381.04</v>
+        <v>442.72</v>
       </c>
       <c r="F14">
-        <v>9.9</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G14">
-        <v>18.7</v>
+        <v>41.2</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
         <v>100</v>
@@ -4139,28 +4175,28 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>96.85499999999999</v>
+        <v>95.804</v>
       </c>
       <c r="E15">
-        <v>387.42</v>
+        <v>479.02</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G15">
-        <v>41.5</v>
+        <v>40.6</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4175,19 +4211,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4198,16 +4234,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4218,16 +4254,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4238,16 +4274,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4261,13 +4297,13 @@
         <v>59</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4278,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -4287,7 +4323,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4298,7 +4334,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -4307,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4315,19 +4351,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4335,19 +4371,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9">
-        <v>-2</v>
-      </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4358,16 +4394,16 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4375,19 +4411,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D11">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4395,19 +4431,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4418,16 +4454,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4435,19 +4471,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
         <v>54</v>
       </c>
       <c r="D14">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4455,19 +4491,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D15">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4477,27 +4513,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4513,11 +4552,14 @@
       <c r="E2">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -4533,11 +4575,14 @@
       <c r="E3">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -4553,11 +4598,14 @@
       <c r="E4">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4573,11 +4621,14 @@
       <c r="E5">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -4593,11 +4644,14 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -4613,51 +4667,60 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>-1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>-2</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>-4</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>-3</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="B9">
-        <v>-1</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>-2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -4673,51 +4736,60 @@
       <c r="E10">
         <v>-3</v>
       </c>
-      <c r="F10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10">
+        <v>-2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>-7</v>
+      </c>
+      <c r="F11">
+        <v>-7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>-3</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>-1</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>-3</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>-6</v>
       </c>
-      <c r="F11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>-7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12">
+        <v>-12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -4733,48 +4805,57 @@
       <c r="E13">
         <v>-9</v>
       </c>
-      <c r="F13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13">
+        <v>-14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>-4</v>
+      </c>
+      <c r="C14">
+        <v>-9</v>
+      </c>
+      <c r="D14">
+        <v>-17</v>
+      </c>
+      <c r="E14">
+        <v>-17</v>
+      </c>
+      <c r="F14">
+        <v>-15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>-4</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>-15</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>-16</v>
       </c>
-      <c r="F14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15">
-        <v>-4</v>
-      </c>
-      <c r="C15">
-        <v>-9</v>
-      </c>
-      <c r="D15">
-        <v>-17</v>
-      </c>
-      <c r="E15">
-        <v>-17</v>
-      </c>
-      <c r="F15" t="s">
-        <v>114</v>
+      <c r="F15">
+        <v>-16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="130">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -67,22 +67,25 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -166,6 +169,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -190,13 +196,16 @@
     <t>nicholas spadaro</t>
   </si>
   <si>
+    <t>Brendan Fanning</t>
+  </si>
+  <si>
+    <t>Antonio  Spadaro</t>
+  </si>
+  <si>
     <t>Kathy Dillon</t>
   </si>
   <si>
-    <t>Brendan Fanning</t>
-  </si>
-  <si>
-    <t>Antonio  Spadaro</t>
+    <t>gabriella spadaro</t>
   </si>
   <si>
     <t>Zachary Dillon</t>
@@ -205,24 +214,21 @@
     <t>Marissa Rodriguez</t>
   </si>
   <si>
-    <t>gabriella spadaro</t>
-  </si>
-  <si>
     <t>Sal Spadaro</t>
   </si>
   <si>
+    <t>Mikaela Mitcho</t>
+  </si>
+  <si>
     <t>Ryan Lesiak</t>
   </si>
   <si>
+    <t>Lawrence Rosello</t>
+  </si>
+  <si>
     <t>Michael Dillon</t>
   </si>
   <si>
-    <t>Mikaela Mitcho</t>
-  </si>
-  <si>
-    <t>Lawrence Rosello</t>
-  </si>
-  <si>
     <t>Stephanie Mattei</t>
   </si>
   <si>
@@ -253,73 +259,70 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>10.8-3.1-0.1</t>
-  </si>
-  <si>
-    <t>11.3-2.7-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.8-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>11.2-2.7-0.1</t>
+  </si>
+  <si>
+    <t>11.1-2.8-0.1</t>
   </si>
   <si>
     <t>7.8-6.1-0.1</t>
   </si>
   <si>
-    <t>7.3-6.6-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>7.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>7.1-6.8-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
   </si>
   <si>
     <t>4.0-9.9-0.1</t>
   </si>
   <si>
-    <t>3.3-10.6-0.1</t>
-  </si>
-  <si>
-    <t>3.0-10.9-0.1</t>
+    <t>4.1-9.8-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>12-2</t>
-  </si>
-  <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>5-9</t>
   </si>
   <si>
     <t>4-10</t>
@@ -337,25 +340,40 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑2</t>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑11</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↓8</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓7</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -371,6 +389,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -807,13 +828,13 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -828,7 +849,7 @@
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
         <v>14</v>
@@ -837,7 +858,7 @@
         <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O2" t="s">
         <v>14</v>
@@ -857,34 +878,34 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" t="s">
         <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
       </c>
       <c r="O3" t="s">
         <v>14</v>
@@ -931,7 +952,7 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="s">
         <v>15</v>
@@ -948,13 +969,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -969,16 +990,16 @@
         <v>14</v>
       </c>
       <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" t="s">
         <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" t="s">
-        <v>14</v>
       </c>
       <c r="O5" t="s">
         <v>15</v>
@@ -989,46 +1010,46 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1036,46 +1057,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
       <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" t="s">
         <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>14</v>
       </c>
       <c r="M7" t="s">
         <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1083,34 +1104,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
@@ -1119,10 +1140,10 @@
         <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1130,46 +1151,46 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" t="s">
         <v>17</v>
       </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>16</v>
       </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1183,13 +1204,13 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -1204,7 +1225,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -1213,7 +1234,7 @@
         <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
         <v>15</v>
@@ -1227,22 +1248,22 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -1251,19 +1272,19 @@
         <v>14</v>
       </c>
       <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" t="s">
         <v>16</v>
       </c>
-      <c r="L11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" t="s">
-        <v>14</v>
-      </c>
       <c r="O11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1271,46 +1292,46 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
         <v>15</v>
       </c>
       <c r="N12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1318,46 +1339,46 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s">
         <v>16</v>
       </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
       <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" t="s">
+        <v>17</v>
+      </c>
+      <c r="O13" t="s">
         <v>16</v>
-      </c>
-      <c r="K13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" t="s">
-        <v>16</v>
-      </c>
-      <c r="O13" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1371,40 +1392,40 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
         <v>15</v>
       </c>
       <c r="N14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1412,25 +1433,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -1442,16 +1463,16 @@
         <v>14</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1461,30 +1482,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1544,22 +1565,22 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
       <c r="E4">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="F4">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="G4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -1573,22 +1594,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="F5">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G5">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1599,22 +1620,22 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>-16</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1622,25 +1643,25 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>-15</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1648,25 +1669,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="F8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1674,25 +1695,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1703,22 +1724,48 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>-9</v>
+      </c>
+      <c r="F10">
+        <v>-4</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
-      <c r="E10">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>12</v>
-      </c>
-      <c r="G10">
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>-3</v>
+      </c>
+      <c r="G11">
         <v>3</v>
       </c>
-      <c r="H10" t="s">
-        <v>5</v>
+      <c r="H11" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1733,13 +1780,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1747,13 +1794,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>1.5</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1761,13 +1808,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1.785714285714286</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1775,10 +1822,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1789,13 +1836,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2.142857142857143</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1803,13 +1850,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>2.214285714285714</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1817,10 +1864,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>2.428571428571428</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1831,13 +1878,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>2.428571428571428</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1848,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1859,10 +1906,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>2.571428571428572</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1876,10 +1923,10 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.571428571428572</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1887,13 +1934,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>2.571428571428572</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1904,7 +1951,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>3.214285714285714</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1918,10 +1965,10 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>3.428571428571428</v>
+        <v>4.357142857142857</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1932,10 +1979,10 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>3.642857142857143</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1950,16 +1997,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1970,13 +2017,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>4.142857142857143</v>
+        <v>4.785714285714286</v>
       </c>
       <c r="D2">
-        <v>0.1428571428571432</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1987,13 +2034,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>3.714285714285714</v>
+        <v>4.642857142857143</v>
       </c>
       <c r="D3">
-        <v>-0.2857142857142856</v>
+        <v>-0.3571428571428568</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2004,10 +2051,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>3.142857142857143</v>
+        <v>3.928571428571428</v>
       </c>
       <c r="D4">
-        <v>0.1428571428571428</v>
+        <v>0.9285714285714284</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -2018,16 +2065,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2.857142857142857</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="D5">
-        <v>0.8571428571428572</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2035,13 +2082,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>2.785714285714286</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D6">
-        <v>-0.2142857142857144</v>
+        <v>0.2142857142857144</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -2052,13 +2099,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>2.714285714285714</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="D7">
-        <v>-0.2857142857142856</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -2069,16 +2116,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>2.571428571428572</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D8">
-        <v>-0.4285714285714284</v>
+        <v>-2.071428571428572</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2086,16 +2133,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>2.428571428571428</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="D9">
-        <v>0.4285714285714284</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2103,16 +2150,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>2.357142857142857</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D10">
-        <v>-1.642857142857143</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2123,13 +2170,13 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>2.071428571428572</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D11">
-        <v>-0.9285714285714284</v>
+        <v>-1.428571428571428</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2140,10 +2187,10 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>2.071428571428572</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D12">
-        <v>0.07142857142857162</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2157,13 +2204,13 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>1.571428571428571</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D13">
-        <v>1.571428571428571</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2174,13 +2221,13 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>1.428571428571429</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D14">
-        <v>0.4285714285714286</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2197,7 +2244,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2212,52 +2259,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2265,28 +2312,28 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>31.3</v>
+        <v>49.9</v>
       </c>
       <c r="C2">
-        <v>53.6</v>
+        <v>42.7</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="E2">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="F2">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2315,28 +2362,28 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>65.3</v>
+        <v>48.5</v>
       </c>
       <c r="C3">
-        <v>25.4</v>
+        <v>44.3</v>
       </c>
       <c r="D3">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="E3">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2365,299 +2412,299 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C4">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>23.3</v>
+        <v>19.2</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>19.3</v>
       </c>
       <c r="F4">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="G4">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
       <c r="I4">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="K4">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="L4">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>94</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="C5">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="D5">
-        <v>15.8</v>
+        <v>20.4</v>
       </c>
       <c r="E5">
-        <v>17.4</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="G5">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="I5">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="M5">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>90.40000000000001</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C6">
         <v>3.3</v>
       </c>
       <c r="D6">
-        <v>17.8</v>
+        <v>15.4</v>
       </c>
       <c r="E6">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="F6">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="G6">
-        <v>14.9</v>
+        <v>11.6</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="I6">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="L6">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="M6">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="N6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>86.5</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>0.2</v>
-      </c>
-      <c r="C7">
-        <v>3.1</v>
-      </c>
       <c r="D7">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="F7">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="G7">
         <v>13.9</v>
       </c>
       <c r="H7">
-        <v>13.5</v>
+        <v>11.2</v>
       </c>
       <c r="I7">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="J7">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="L7">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M7">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="N7">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>84</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F8">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="G8">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="H8">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="I8">
-        <v>15.3</v>
+        <v>13</v>
       </c>
       <c r="J8">
-        <v>13.1</v>
+        <v>14.6</v>
       </c>
       <c r="K8">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="L8">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="M8">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="N8">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="O8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P8">
-        <v>69</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="E9">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="F9">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <v>14.9</v>
+        <v>11.8</v>
       </c>
       <c r="I9">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J9">
-        <v>13.8</v>
+        <v>12.2</v>
       </c>
       <c r="K9">
-        <v>8.9</v>
+        <v>11.6</v>
       </c>
       <c r="L9">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="M9">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>68.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2665,99 +2712,99 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
+        <v>0.5</v>
+      </c>
+      <c r="D10">
+        <v>3.8</v>
+      </c>
+      <c r="E10">
+        <v>6.9</v>
+      </c>
+      <c r="F10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G10">
+        <v>11.2</v>
+      </c>
+      <c r="H10">
+        <v>12.7</v>
+      </c>
+      <c r="I10">
+        <v>13.2</v>
+      </c>
+      <c r="J10">
+        <v>14.6</v>
+      </c>
+      <c r="K10">
+        <v>12.5</v>
+      </c>
+      <c r="L10">
+        <v>10.4</v>
+      </c>
+      <c r="M10">
+        <v>3.5</v>
+      </c>
+      <c r="N10">
+        <v>1.6</v>
+      </c>
+      <c r="O10">
         <v>0.2</v>
       </c>
-      <c r="D10">
-        <v>1.3</v>
-      </c>
-      <c r="E10">
-        <v>3.6</v>
-      </c>
-      <c r="F10">
-        <v>7.4</v>
-      </c>
-      <c r="G10">
-        <v>8.6</v>
-      </c>
-      <c r="H10">
-        <v>12.3</v>
-      </c>
-      <c r="I10">
-        <v>14.8</v>
-      </c>
-      <c r="J10">
-        <v>16.5</v>
-      </c>
-      <c r="K10">
-        <v>15.9</v>
-      </c>
-      <c r="L10">
-        <v>13</v>
-      </c>
-      <c r="M10">
-        <v>4.7</v>
-      </c>
-      <c r="N10">
-        <v>1.3</v>
-      </c>
-      <c r="O10">
-        <v>0.4</v>
-      </c>
       <c r="P10">
-        <v>48.2</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0.7</v>
+      </c>
+      <c r="D11">
+        <v>5.5</v>
+      </c>
+      <c r="E11">
+        <v>7.7</v>
+      </c>
+      <c r="F11">
         <v>7</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0.7</v>
-      </c>
-      <c r="E11">
-        <v>1.9</v>
-      </c>
-      <c r="F11">
-        <v>2.2</v>
-      </c>
       <c r="G11">
-        <v>4.5</v>
+        <v>11.1</v>
       </c>
       <c r="H11">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="I11">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="J11">
-        <v>17.3</v>
+        <v>14.2</v>
       </c>
       <c r="K11">
-        <v>22.2</v>
+        <v>14.2</v>
       </c>
       <c r="L11">
-        <v>20</v>
+        <v>9.9</v>
       </c>
       <c r="M11">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>29.2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2768,51 +2815,51 @@
         <v>0</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>0.3</v>
       </c>
-      <c r="D12">
-        <v>0.6</v>
-      </c>
       <c r="E12">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="F12">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="G12">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="I12">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="J12">
-        <v>15.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K12">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="L12">
-        <v>20.2</v>
+        <v>26.9</v>
       </c>
       <c r="M12">
-        <v>11.8</v>
+        <v>21.4</v>
       </c>
       <c r="N12">
-        <v>5.4</v>
+        <v>12.4</v>
       </c>
       <c r="O12">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="P12">
-        <v>26.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2827,42 +2874,42 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G13">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H13">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I13">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J13">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="K13">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="L13">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="M13">
-        <v>33.4</v>
+        <v>28.4</v>
       </c>
       <c r="N13">
-        <v>26.8</v>
+        <v>32.4</v>
       </c>
       <c r="O13">
-        <v>16.3</v>
+        <v>15.5</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2880,39 +2927,39 @@
         <v>0.1</v>
       </c>
       <c r="G14">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H14">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I14">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="K14">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="L14">
-        <v>6.8</v>
+        <v>17.2</v>
       </c>
       <c r="M14">
-        <v>18.2</v>
+        <v>26.6</v>
       </c>
       <c r="N14">
-        <v>30.1</v>
+        <v>32.4</v>
       </c>
       <c r="O14">
-        <v>41.2</v>
+        <v>12.3</v>
       </c>
       <c r="P14">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2930,34 +2977,34 @@
         <v>0</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0.1</v>
       </c>
-      <c r="H15">
-        <v>0.3</v>
-      </c>
       <c r="I15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="K15">
+        <v>1.5</v>
+      </c>
+      <c r="L15">
         <v>2.3</v>
       </c>
-      <c r="L15">
-        <v>4.9</v>
-      </c>
       <c r="M15">
-        <v>18.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N15">
-        <v>32.1</v>
+        <v>17.8</v>
       </c>
       <c r="O15">
-        <v>40.6</v>
+        <v>70</v>
       </c>
       <c r="P15">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2967,35 +3014,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -3004,16 +3054,19 @@
         <v>100</v>
       </c>
       <c r="E2">
+        <v>99.7</v>
+      </c>
+      <c r="F2">
         <v>99.90000000000001</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3035,281 +3088,320 @@
       <c r="G3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>96.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F4">
-        <v>93.30000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="G4">
-        <v>91.60000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>91.5</v>
+      </c>
+      <c r="H4">
+        <v>88.90000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.3</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>6.9</v>
+      </c>
+      <c r="E5">
+        <v>71.3</v>
+      </c>
+      <c r="F5">
+        <v>87.7</v>
+      </c>
+      <c r="G5">
+        <v>85.39999999999999</v>
+      </c>
+      <c r="H5">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+      <c r="C6">
+        <v>6.4</v>
+      </c>
+      <c r="D6">
+        <v>4.7</v>
+      </c>
+      <c r="E6">
+        <v>26.6</v>
+      </c>
+      <c r="F6">
+        <v>71.7</v>
+      </c>
+      <c r="G6">
+        <v>81.69999999999999</v>
+      </c>
+      <c r="H6">
+        <v>85.39999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="C7">
+        <v>87</v>
+      </c>
+      <c r="D7">
+        <v>89.8</v>
+      </c>
+      <c r="E7">
+        <v>62</v>
+      </c>
+      <c r="F7">
+        <v>32.8</v>
+      </c>
+      <c r="G7">
+        <v>77.7</v>
+      </c>
+      <c r="H7">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>45.4</v>
-      </c>
-      <c r="C5">
-        <v>98.7</v>
-      </c>
-      <c r="D5">
-        <v>99</v>
-      </c>
-      <c r="E5">
-        <v>81.2</v>
-      </c>
-      <c r="F5">
-        <v>89</v>
-      </c>
-      <c r="G5">
-        <v>89.60000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>0.3</v>
-      </c>
-      <c r="C6">
-        <v>9.4</v>
-      </c>
-      <c r="D6">
-        <v>7.1</v>
-      </c>
-      <c r="E6">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F6">
-        <v>86.2</v>
-      </c>
-      <c r="G6">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
+      <c r="B8">
+        <v>45.2</v>
+      </c>
+      <c r="C8">
+        <v>98.5</v>
+      </c>
+      <c r="D8">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E8">
+        <v>81</v>
+      </c>
+      <c r="F8">
+        <v>89.8</v>
+      </c>
+      <c r="G8">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="H8">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C7">
-        <v>66.10000000000001</v>
-      </c>
-      <c r="D7">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="E7">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="F7">
-        <v>78.7</v>
-      </c>
-      <c r="G7">
-        <v>85.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>0.3</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-      <c r="D8">
-        <v>5.7</v>
-      </c>
-      <c r="E8">
-        <v>26.9</v>
-      </c>
-      <c r="F8">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="G8">
-        <v>68.60000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B9">
-        <v>4.8</v>
+        <v>100</v>
       </c>
       <c r="C9">
+        <v>69.3</v>
+      </c>
+      <c r="D9">
+        <v>99.2</v>
+      </c>
+      <c r="E9">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="F9">
+        <v>77.8</v>
+      </c>
+      <c r="G9">
+        <v>60.5</v>
+      </c>
+      <c r="H9">
+        <v>65.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
         <v>39</v>
       </c>
-      <c r="D9">
-        <v>91.7</v>
-      </c>
-      <c r="E9">
-        <v>96.8</v>
-      </c>
-      <c r="F9">
-        <v>66.60000000000001</v>
-      </c>
-      <c r="G9">
-        <v>66.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
+      <c r="D10">
+        <v>92.30000000000001</v>
+      </c>
+      <c r="E10">
+        <v>96.2</v>
+      </c>
+      <c r="F10">
+        <v>66.2</v>
+      </c>
+      <c r="G10">
+        <v>50.1</v>
+      </c>
+      <c r="H10">
+        <v>55.50000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>99.2</v>
-      </c>
-      <c r="C10">
-        <v>24.5</v>
-      </c>
-      <c r="D10">
-        <v>9.4</v>
-      </c>
-      <c r="E10">
-        <v>19.7</v>
-      </c>
-      <c r="F10">
-        <v>43.2</v>
-      </c>
-      <c r="G10">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B11">
-        <v>75.5</v>
+        <v>98.8</v>
       </c>
       <c r="C11">
-        <v>88.09999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="D11">
-        <v>90.2</v>
+        <v>11.5</v>
       </c>
       <c r="E11">
-        <v>61.9</v>
+        <v>21.4</v>
       </c>
       <c r="F11">
-        <v>28.4</v>
+        <v>43.8</v>
       </c>
       <c r="G11">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>63.1</v>
+      </c>
+      <c r="H11">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>0.1</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0.3</v>
       </c>
       <c r="E12">
         <v>18.8</v>
       </c>
       <c r="F12">
-        <v>34.1</v>
+        <v>32.6</v>
       </c>
       <c r="G12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>17.7</v>
+      </c>
+      <c r="H12">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>94.69999999999999</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="C13">
-        <v>95.19999999999999</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="D13">
-        <v>69.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E13">
-        <v>17.3</v>
+        <v>15.6</v>
       </c>
       <c r="F13">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="G13">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>3.5</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B14">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
       <c r="C14">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="D14">
-        <v>4.9</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="E14">
-        <v>4.399999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="F14">
-        <v>0.7000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G14">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>3.6</v>
+      </c>
+      <c r="H14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>71.7</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="C15">
-        <v>70</v>
+        <v>68.89999999999999</v>
       </c>
       <c r="D15">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="E15">
-        <v>7.1</v>
+        <v>7.399999999999999</v>
       </c>
       <c r="F15">
-        <v>0.8999999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="G15">
-        <v>0.8999999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="H15">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -3324,28 +3416,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3356,25 +3448,25 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>107.14</v>
+        <v>105.41</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>117.82</v>
+        <v>115.35</v>
       </c>
       <c r="G2">
-        <v>0.578</v>
+        <v>0.583</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>11.1</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3382,28 +3474,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>106.15</v>
+        <v>101.28</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>111.28</v>
+        <v>112.24</v>
       </c>
       <c r="G3">
-        <v>0.444</v>
+        <v>0.521</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3411,28 +3503,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4">
-        <v>103.13</v>
+        <v>108.28</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>111.38</v>
+        <v>108.94</v>
       </c>
       <c r="G4">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3440,28 +3532,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5">
-        <v>114.68</v>
+        <v>112.21</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5">
-        <v>110.33</v>
+        <v>108.31</v>
       </c>
       <c r="G5">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3469,28 +3561,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>85.12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>107.95</v>
+      </c>
+      <c r="G6">
+        <v>0.458</v>
+      </c>
+      <c r="H6">
+        <v>4.4</v>
+      </c>
+      <c r="I6">
         <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6">
-        <v>103.38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>109.82</v>
-      </c>
-      <c r="G6">
-        <v>0.467</v>
-      </c>
-      <c r="H6">
-        <v>2.9</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3498,28 +3590,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7">
-        <v>117.78</v>
+        <v>100.75</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>110.36</v>
+        <v>109.41</v>
       </c>
       <c r="G7">
-        <v>0.533</v>
+        <v>0.521</v>
       </c>
       <c r="H7">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3527,28 +3619,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D8">
-        <v>88.54000000000001</v>
+        <v>117.44</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>108.72</v>
+        <v>108.94</v>
       </c>
       <c r="G8">
-        <v>0.467</v>
+        <v>0.542</v>
       </c>
       <c r="H8">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3559,25 +3651,25 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9">
-        <v>107.6</v>
+        <v>104.82</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9">
-        <v>109.39</v>
+        <v>105.5</v>
       </c>
       <c r="G9">
-        <v>0.489</v>
+        <v>0.438</v>
       </c>
       <c r="H9">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3585,28 +3677,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10">
-        <v>95.23999999999999</v>
+        <v>97.34</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>109.2</v>
+        <v>105.35</v>
       </c>
       <c r="G10">
-        <v>0.489</v>
+        <v>0.521</v>
       </c>
       <c r="H10">
-        <v>-1.8</v>
+        <v>-4.4</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3614,28 +3706,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>112.44</v>
+        <v>97.2</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>108.23</v>
+        <v>104.84</v>
       </c>
       <c r="G11">
-        <v>0.511</v>
+        <v>0.438</v>
       </c>
       <c r="H11">
-        <v>-2.9</v>
+        <v>-5</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3643,28 +3735,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12">
-        <v>95.8</v>
+        <v>128.44</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>107.01</v>
+        <v>107.06</v>
       </c>
       <c r="G12">
-        <v>0.533</v>
+        <v>0.583</v>
       </c>
       <c r="H12">
-        <v>-4.8</v>
+        <v>-6.9</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3672,28 +3764,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13">
-        <v>133.2</v>
+        <v>105.68</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>108.83</v>
+        <v>103.98</v>
       </c>
       <c r="G13">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H13">
-        <v>-5.1</v>
+        <v>-7.2</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3704,25 +3796,25 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14">
-        <v>117.63</v>
+        <v>112.89</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>104.1</v>
+        <v>102.81</v>
       </c>
       <c r="G14">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H14">
-        <v>-7.1</v>
+        <v>-7.2</v>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3733,25 +3825,25 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15">
-        <v>128.08</v>
+        <v>127.8</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>104.35</v>
+        <v>103.97</v>
       </c>
       <c r="G15">
-        <v>0.489</v>
+        <v>0.521</v>
       </c>
       <c r="H15">
-        <v>-7.9</v>
+        <v>-8.9</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3766,31 +3858,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3798,16 +3890,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>128.084</v>
+        <v>127.7966666666667</v>
       </c>
       <c r="E2">
-        <v>640.42</v>
+        <v>766.78</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -3816,10 +3908,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3827,16 +3919,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D3">
-        <v>133.2</v>
+        <v>128.4366666666667</v>
       </c>
       <c r="E3">
-        <v>666</v>
+        <v>770.62</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -3845,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3856,173 +3948,173 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>117.784</v>
+        <v>117.4366666666667</v>
       </c>
       <c r="E4">
-        <v>588.9200000000001</v>
+        <v>704.6200000000001</v>
       </c>
       <c r="F4">
-        <v>94</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>114.684</v>
+        <v>112.8866666666667</v>
       </c>
       <c r="E5">
-        <v>573.4200000000001</v>
+        <v>677.3199999999999</v>
       </c>
       <c r="F5">
-        <v>90.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D6">
-        <v>117.628</v>
+        <v>105.4133333333333</v>
       </c>
       <c r="E6">
-        <v>588.14</v>
+        <v>632.48</v>
       </c>
       <c r="F6">
-        <v>86.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>112.436</v>
+        <v>112.2066666666667</v>
       </c>
       <c r="E7">
-        <v>562.1799999999999</v>
+        <v>673.24</v>
       </c>
       <c r="F7">
-        <v>84</v>
+        <v>81.3</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>107.604</v>
+        <v>108.2766666666667</v>
       </c>
       <c r="E8">
-        <v>538.02</v>
+        <v>649.6600000000001</v>
       </c>
       <c r="F8">
-        <v>69</v>
+        <v>65.10000000000001</v>
       </c>
       <c r="G8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>107.14</v>
+        <v>105.68</v>
       </c>
       <c r="E9">
-        <v>535.7</v>
+        <v>634.0799999999999</v>
       </c>
       <c r="F9">
-        <v>68.2</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4030,54 +4122,54 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D10">
-        <v>103.132</v>
+        <v>101.2766666666667</v>
       </c>
       <c r="E10">
-        <v>515.6600000000001</v>
+        <v>607.6600000000001</v>
       </c>
       <c r="F10">
-        <v>48.2</v>
+        <v>57.2</v>
       </c>
       <c r="G10">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>106.148</v>
+        <v>104.8233333333333</v>
       </c>
       <c r="E11">
-        <v>530.74</v>
+        <v>628.9399999999999</v>
       </c>
       <c r="F11">
-        <v>29.2</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="G11">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
         <v>98</v>
@@ -4088,83 +4180,83 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12">
-        <v>103.384</v>
+        <v>100.75</v>
       </c>
       <c r="E12">
-        <v>516.92</v>
+        <v>604.5</v>
       </c>
       <c r="F12">
-        <v>26.5</v>
+        <v>12.7</v>
       </c>
       <c r="G12">
-        <v>0.8999999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C13">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D13">
-        <v>95.244</v>
+        <v>97.33999999999999</v>
       </c>
       <c r="E13">
-        <v>476.22</v>
+        <v>584.04</v>
       </c>
       <c r="F13">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="G13">
-        <v>16.3</v>
+        <v>15.5</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C14">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D14">
-        <v>88.544</v>
+        <v>97.20333333333333</v>
       </c>
       <c r="E14">
-        <v>442.72</v>
+        <v>583.22</v>
       </c>
       <c r="F14">
-        <v>0.8999999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="G14">
-        <v>41.2</v>
+        <v>12.3</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I14" t="s">
         <v>100</v>
@@ -4172,31 +4264,31 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D15">
-        <v>95.804</v>
+        <v>85.11999999999999</v>
       </c>
       <c r="E15">
-        <v>479.02</v>
+        <v>510.72</v>
       </c>
       <c r="F15">
-        <v>0.7000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G15">
-        <v>40.6</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4211,19 +4303,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4231,19 +4323,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4251,19 +4343,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4271,19 +4363,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4291,7 +4383,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>59</v>
@@ -4303,7 +4395,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4311,19 +4403,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4331,19 +4423,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
         <v>63</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4351,19 +4443,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4371,19 +4463,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4391,19 +4483,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4411,19 +4503,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D11">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4431,19 +4523,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4451,19 +4543,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4471,19 +4563,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D14">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4494,16 +4586,16 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4513,329 +4605,371 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>-5</v>
+      </c>
+      <c r="C5">
+        <v>-9</v>
+      </c>
+      <c r="D5">
+        <v>-2</v>
+      </c>
+      <c r="E5">
+        <v>-3</v>
+      </c>
+      <c r="F5">
+        <v>-2</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>-1</v>
+      </c>
+      <c r="C7">
+        <v>-3</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>-4</v>
+      </c>
+      <c r="D8">
+        <v>-3</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>-7</v>
+      </c>
+      <c r="F9">
+        <v>-7</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>-1</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>-2</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>-3</v>
+      </c>
+      <c r="H10" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>-6</v>
+      </c>
+      <c r="H11" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>-7</v>
+      </c>
+      <c r="C12">
+        <v>-13</v>
+      </c>
+      <c r="D12">
+        <v>-15</v>
+      </c>
+      <c r="E12">
+        <v>-9</v>
+      </c>
+      <c r="F12">
+        <v>-14</v>
+      </c>
+      <c r="G12">
+        <v>-15</v>
+      </c>
+      <c r="H12" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>-4</v>
+      </c>
+      <c r="C13">
+        <v>-9</v>
+      </c>
+      <c r="D13">
+        <v>-17</v>
+      </c>
+      <c r="E13">
+        <v>-17</v>
+      </c>
+      <c r="F13">
+        <v>-15</v>
+      </c>
+      <c r="G13">
+        <v>-18</v>
+      </c>
+      <c r="H13" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2">
-        <v>18</v>
-      </c>
-      <c r="E2">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>11</v>
-      </c>
-      <c r="F4">
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6">
+      <c r="B14">
+        <v>-3</v>
+      </c>
+      <c r="C14">
         <v>-1</v>
       </c>
-      <c r="C6">
+      <c r="D14">
         <v>-3</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>-1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>-2</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>-4</v>
-      </c>
-      <c r="D9">
-        <v>-3</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>-5</v>
-      </c>
-      <c r="C10">
-        <v>-9</v>
-      </c>
-      <c r="D10">
-        <v>-2</v>
-      </c>
-      <c r="E10">
-        <v>-3</v>
-      </c>
-      <c r="F10">
-        <v>-2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>-7</v>
-      </c>
-      <c r="F11">
-        <v>-7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>-3</v>
-      </c>
-      <c r="C12">
-        <v>-1</v>
-      </c>
-      <c r="D12">
-        <v>-3</v>
-      </c>
-      <c r="E12">
+      <c r="E14">
         <v>-6</v>
       </c>
-      <c r="F12">
+      <c r="F14">
         <v>-12</v>
       </c>
-      <c r="G12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>-7</v>
-      </c>
-      <c r="C13">
-        <v>-13</v>
-      </c>
-      <c r="D13">
-        <v>-15</v>
-      </c>
-      <c r="E13">
-        <v>-9</v>
-      </c>
-      <c r="F13">
-        <v>-14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14">
-        <v>-4</v>
-      </c>
-      <c r="C14">
-        <v>-9</v>
-      </c>
-      <c r="D14">
-        <v>-17</v>
-      </c>
-      <c r="E14">
-        <v>-17</v>
-      </c>
-      <c r="F14">
-        <v>-15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="G14">
+        <v>-19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -4854,8 +4988,11 @@
       <c r="F15">
         <v>-16</v>
       </c>
-      <c r="G15" t="s">
-        <v>106</v>
+      <c r="G15">
+        <v>-21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="134">
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
@@ -67,25 +67,28 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -172,6 +175,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -193,27 +199,27 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Brendan Fanning</t>
+  </si>
+  <si>
     <t>nicholas spadaro</t>
   </si>
   <si>
-    <t>Brendan Fanning</t>
+    <t>Kathy Dillon</t>
+  </si>
+  <si>
+    <t>Marissa Rodriguez</t>
+  </si>
+  <si>
+    <t>Zachary Dillon</t>
+  </si>
+  <si>
+    <t>gabriella spadaro</t>
   </si>
   <si>
     <t>Antonio  Spadaro</t>
   </si>
   <si>
-    <t>Kathy Dillon</t>
-  </si>
-  <si>
-    <t>gabriella spadaro</t>
-  </si>
-  <si>
-    <t>Zachary Dillon</t>
-  </si>
-  <si>
-    <t>Marissa Rodriguez</t>
-  </si>
-  <si>
     <t>Sal Spadaro</t>
   </si>
   <si>
@@ -226,15 +232,15 @@
     <t>Lawrence Rosello</t>
   </si>
   <si>
+    <t>Stephanie Mattei</t>
+  </si>
+  <si>
+    <t>Josh Formola</t>
+  </si>
+  <si>
     <t>Michael Dillon</t>
   </si>
   <si>
-    <t>Stephanie Mattei</t>
-  </si>
-  <si>
-    <t>Josh Formola</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -259,63 +265,69 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>11.2-2.7-0.1</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>10.4-3.5-0.1</t>
+  </si>
+  <si>
+    <t>9.8-4.2-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.9-0.1</t>
+  </si>
+  <si>
+    <t>8.0-6.0-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
   </si>
   <si>
     <t>7.8-6.1-0.1</t>
   </si>
   <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>7.1-6.8-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9-0.1</t>
-  </si>
-  <si>
-    <t>4.1-9.8-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.2-0.1</t>
+  </si>
+  <si>
+    <t>3.8-10.2-0.1</t>
+  </si>
+  <si>
+    <t>3.6-10.3-0.1</t>
+  </si>
+  <si>
+    <t>2.5-11.5-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
+    <t>10-4</t>
+  </si>
+  <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>8-6</t>
   </si>
   <si>
@@ -331,6 +343,9 @@
     <t>3-11</t>
   </si>
   <si>
+    <t>2-12</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -340,40 +355,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑9</t>
-  </si>
-  <si>
-    <t>↑1</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑5</t>
   </si>
   <si>
     <t>↑8</t>
   </si>
   <si>
-    <t>↑11</t>
-  </si>
-  <si>
-    <t>↓6</t>
+    <t>↓4</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↓8</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓7</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -392,6 +401,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -828,7 +840,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -846,10 +858,10 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
         <v>14</v>
@@ -858,7 +870,7 @@
         <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="s">
         <v>14</v>
@@ -875,7 +887,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -899,13 +911,13 @@
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M3" t="s">
         <v>14</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O3" t="s">
         <v>14</v>
@@ -916,10 +928,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -928,34 +940,34 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
         <v>15</v>
       </c>
-      <c r="H4" t="s">
+      <c r="M4" t="s">
         <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" t="s">
-        <v>15</v>
       </c>
       <c r="N4" t="s">
         <v>17</v>
       </c>
       <c r="O4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -963,46 +975,46 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" t="s">
         <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1010,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1034,22 +1046,22 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" t="s">
         <v>16</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
       </c>
       <c r="M6" t="s">
         <v>18</v>
       </c>
       <c r="N6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" t="s">
         <v>16</v>
-      </c>
-      <c r="O6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1057,25 +1069,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -1084,19 +1096,19 @@
         <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1113,31 +1125,31 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N8" t="s">
         <v>19</v>
@@ -1163,31 +1175,31 @@
         <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
         <v>14</v>
       </c>
       <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s">
         <v>17</v>
-      </c>
-      <c r="K9" t="s">
-        <v>16</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
         <v>15</v>
@@ -1198,13 +1210,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -1213,7 +1225,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -1222,22 +1234,22 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" t="s">
         <v>16</v>
       </c>
-      <c r="L10" t="s">
-        <v>15</v>
-      </c>
       <c r="M10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O10" t="s">
         <v>16</v>
-      </c>
-      <c r="O10" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1248,7 +1260,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1257,22 +1269,22 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
         <v>15</v>
       </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L11" t="s">
         <v>14</v>
@@ -1281,10 +1293,10 @@
         <v>15</v>
       </c>
       <c r="N11" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" t="s">
         <v>16</v>
-      </c>
-      <c r="O11" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1292,19 +1304,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
@@ -1316,22 +1328,22 @@
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
       <c r="M12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" t="s">
         <v>15</v>
       </c>
-      <c r="N12" t="s">
-        <v>14</v>
-      </c>
       <c r="O12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1339,25 +1351,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -1369,16 +1381,16 @@
         <v>19</v>
       </c>
       <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
         <v>15</v>
-      </c>
-      <c r="M13" t="s">
-        <v>14</v>
       </c>
       <c r="N13" t="s">
         <v>17</v>
       </c>
       <c r="O13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1401,31 +1413,31 @@
         <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
         <v>16</v>
       </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
       <c r="J14" t="s">
         <v>14</v>
       </c>
       <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
         <v>16</v>
-      </c>
-      <c r="L14" t="s">
-        <v>18</v>
       </c>
       <c r="M14" t="s">
         <v>15</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1439,7 +1451,7 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
@@ -1454,13 +1466,13 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" t="s">
         <v>15</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" t="s">
-        <v>14</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1482,30 +1494,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1513,25 +1525,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
       <c r="E2">
+        <v>-20</v>
+      </c>
+      <c r="F2">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2">
-        <v>-16</v>
-      </c>
-      <c r="G2">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1539,25 +1551,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1565,25 +1577,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
         <v>9</v>
       </c>
-      <c r="E4">
-        <v>-3</v>
-      </c>
       <c r="F4">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1591,25 +1603,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>-17</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1620,22 +1632,22 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="F6">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1643,25 +1655,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>-3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>-18</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1669,22 +1681,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="F8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>9</v>
@@ -1695,25 +1707,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>-2</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>-16</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1721,25 +1733,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>-9</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1747,25 +1759,77 @@
         <v>9</v>
       </c>
       <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>-15</v>
+      </c>
+      <c r="F11">
+        <v>-7</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>-3</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-      <c r="H11" t="s">
-        <v>0</v>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>-9</v>
+      </c>
+      <c r="F13">
+        <v>-4</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1780,13 +1844,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1794,10 +1858,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>2.142857142857143</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -1808,13 +1872,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>2.214285714285714</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1822,13 +1886,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>2.428571428571428</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1839,10 +1903,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1850,13 +1914,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>2.642857142857143</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1864,10 +1928,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2.714285714285714</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1878,13 +1942,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.714285714285714</v>
+        <v>3.357142857142857</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1892,10 +1956,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>2.928571428571428</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1906,10 +1970,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>2.928571428571428</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1923,7 +1987,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>3.142857142857143</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -1934,13 +1998,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>3.285714285714286</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1948,13 +2012,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>3.571428571428572</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1965,10 +2029,10 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>4.357142857142857</v>
+        <v>4.928571428571429</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1979,10 +2043,10 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>4.428571428571429</v>
+        <v>5.214285714285714</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1997,16 +2061,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2014,13 +2078,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>4.785714285714286</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="D2">
-        <v>-0.2142857142857144</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -2031,13 +2095,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>4.642857142857143</v>
-      </c>
       <c r="D3">
-        <v>-0.3571428571428568</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -2048,13 +2112,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>3.928571428571428</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="D4">
-        <v>0.9285714285714284</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -2065,13 +2129,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>3.428571428571428</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="D5">
-        <v>0.4285714285714284</v>
+        <v>0.1428571428571432</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -2082,16 +2146,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>3.214285714285714</v>
+        <v>4.071428571428571</v>
       </c>
       <c r="D6">
-        <v>0.2142857142857144</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2099,13 +2163,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>3.142857142857143</v>
+        <v>3.714285714285714</v>
       </c>
       <c r="D7">
-        <v>0.1428571428571428</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -2116,16 +2180,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>2.928571428571428</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="D8">
-        <v>-2.071428571428572</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2133,16 +2197,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>2.785714285714286</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="D9">
-        <v>-0.2142857142857144</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2150,16 +2214,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>2.714285714285714</v>
+        <v>3.357142857142857</v>
       </c>
       <c r="D10">
-        <v>-0.2857142857142856</v>
+        <v>-1.642857142857143</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2167,16 +2231,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>2.571428571428572</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="D11">
-        <v>-1.428571428571428</v>
+        <v>-0.8571428571428572</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2184,16 +2248,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>2.285714285714286</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="D12">
-        <v>0.2857142857142856</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2201,16 +2265,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>2.285714285714286</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D13">
-        <v>1.285714285714286</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2221,10 +2285,10 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>2.142857142857143</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D14">
-        <v>1.142857142857143</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -2259,52 +2323,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2312,31 +2376,31 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>49.9</v>
+        <v>58.3</v>
       </c>
       <c r="C2">
-        <v>42.7</v>
+        <v>25.4</v>
       </c>
       <c r="D2">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E2">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="F2">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2354,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2362,38 +2426,38 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>48.5</v>
+        <v>26.8</v>
       </c>
       <c r="C3">
-        <v>44.3</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>8.9</v>
       </c>
       <c r="F3">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="G3">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="H3">
+        <v>1.3</v>
+      </c>
+      <c r="I3">
+        <v>1.3</v>
+      </c>
+      <c r="J3">
+        <v>1.1</v>
+      </c>
+      <c r="K3">
+        <v>0.3</v>
+      </c>
+      <c r="L3">
         <v>0.1</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
       <c r="M3">
         <v>0</v>
       </c>
@@ -2404,48 +2468,48 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>7.1</v>
+      </c>
+      <c r="C4">
+        <v>12.9</v>
+      </c>
+      <c r="D4">
+        <v>13.5</v>
+      </c>
+      <c r="E4">
+        <v>14.2</v>
+      </c>
+      <c r="F4">
+        <v>14.2</v>
+      </c>
+      <c r="G4">
+        <v>12.5</v>
+      </c>
+      <c r="H4">
         <v>11</v>
       </c>
-      <c r="B4">
-        <v>0.3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-      <c r="D4">
-        <v>19.2</v>
-      </c>
-      <c r="E4">
-        <v>19.3</v>
-      </c>
-      <c r="F4">
-        <v>15.4</v>
-      </c>
-      <c r="G4">
-        <v>12.9</v>
-      </c>
-      <c r="H4">
-        <v>10.8</v>
-      </c>
       <c r="I4">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="K4">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2454,98 +2518,98 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>89.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="C5">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>20.4</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="I5">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="J5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="M5">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="N5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>85.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="C6">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="D6">
-        <v>15.4</v>
+        <v>13.9</v>
       </c>
       <c r="E6">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="F6">
-        <v>14.9</v>
+        <v>11.3</v>
       </c>
       <c r="G6">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="H6">
-        <v>11.4</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K6">
-        <v>6.4</v>
+        <v>9.9</v>
       </c>
       <c r="L6">
         <v>2.2</v>
       </c>
       <c r="M6">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2554,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>82.09999999999999</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2562,99 +2626,99 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7">
+        <v>10.7</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>10.8</v>
+      </c>
+      <c r="G7">
+        <v>12.6</v>
+      </c>
+      <c r="H7">
+        <v>12.7</v>
+      </c>
+      <c r="I7">
+        <v>13.4</v>
+      </c>
+      <c r="J7">
+        <v>11.9</v>
+      </c>
+      <c r="K7">
+        <v>8.6</v>
+      </c>
+      <c r="L7">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>14.1</v>
-      </c>
-      <c r="F7">
-        <v>15.2</v>
-      </c>
-      <c r="G7">
-        <v>13.9</v>
-      </c>
-      <c r="H7">
-        <v>11.2</v>
-      </c>
-      <c r="I7">
-        <v>11.9</v>
-      </c>
-      <c r="J7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K7">
-        <v>6.1</v>
-      </c>
-      <c r="L7">
-        <v>2.6</v>
-      </c>
       <c r="M7">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>81.3</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E8">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="G8">
-        <v>12.8</v>
+        <v>11.9</v>
       </c>
       <c r="H8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J8">
-        <v>14.6</v>
+        <v>10.5</v>
       </c>
       <c r="K8">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="M8">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="N8">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>65.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2662,49 +2726,49 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="E9">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F9">
-        <v>10.7</v>
+        <v>11.7</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="H9">
-        <v>11.8</v>
+        <v>13.1</v>
       </c>
       <c r="I9">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="J9">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="K9">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="L9">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>64</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2712,99 +2776,99 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="D10">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="E10">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="H10">
-        <v>12.7</v>
+        <v>14.3</v>
       </c>
       <c r="I10">
-        <v>13.2</v>
+        <v>14.3</v>
       </c>
       <c r="J10">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="K10">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="L10">
-        <v>10.4</v>
+        <v>3</v>
       </c>
       <c r="M10">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="N10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>57.2</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C11">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E11">
-        <v>7.7</v>
+        <v>4.9</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G11">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="H11">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="I11">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="J11">
-        <v>14.2</v>
+        <v>19.8</v>
       </c>
       <c r="K11">
-        <v>14.2</v>
+        <v>21</v>
       </c>
       <c r="L11">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="M11">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>57</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2818,43 +2882,43 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="I12">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J12">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="K12">
-        <v>16</v>
+        <v>11.6</v>
       </c>
       <c r="L12">
-        <v>26.9</v>
+        <v>43.9</v>
       </c>
       <c r="M12">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="N12">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="O12">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="P12">
-        <v>12.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2874,37 +2938,37 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J13">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K13">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
-        <v>12.7</v>
+        <v>17.2</v>
       </c>
       <c r="M13">
-        <v>28.4</v>
+        <v>41.5</v>
       </c>
       <c r="N13">
-        <v>32.4</v>
+        <v>25.1</v>
       </c>
       <c r="O13">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2924,37 +2988,37 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>0.1</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>0.3</v>
       </c>
-      <c r="H14">
-        <v>1.1</v>
-      </c>
-      <c r="I14">
-        <v>1.1</v>
-      </c>
       <c r="J14">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="K14">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="L14">
-        <v>17.2</v>
+        <v>12.3</v>
       </c>
       <c r="M14">
-        <v>26.6</v>
+        <v>25.2</v>
       </c>
       <c r="N14">
-        <v>32.4</v>
+        <v>43</v>
       </c>
       <c r="O14">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2980,31 +3044,31 @@
         <v>0</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>0.1</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0.1</v>
-      </c>
-      <c r="K15">
+      <c r="L15">
         <v>1.5</v>
       </c>
-      <c r="L15">
-        <v>2.3</v>
-      </c>
       <c r="M15">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="N15">
         <v>17.8</v>
       </c>
       <c r="O15">
-        <v>70</v>
+        <v>73.2</v>
       </c>
       <c r="P15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3014,38 +3078,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>49</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -3054,19 +3121,22 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>99.8</v>
+      </c>
+      <c r="I2">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3089,140 +3159,158 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>99.2</v>
+      </c>
+      <c r="I3">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>96.09999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>6.1</v>
       </c>
       <c r="E4">
-        <v>99.40000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="F4">
-        <v>93.5</v>
+        <v>70.7</v>
       </c>
       <c r="G4">
+        <v>80.5</v>
+      </c>
+      <c r="H4">
+        <v>88.3</v>
+      </c>
+      <c r="I4">
         <v>91.5</v>
       </c>
-      <c r="H4">
-        <v>88.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>42.4</v>
+      </c>
+      <c r="C5">
+        <v>98.8</v>
+      </c>
+      <c r="D5">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E5">
+        <v>80.5</v>
+      </c>
+      <c r="F5">
+        <v>89.3</v>
+      </c>
+      <c r="G5">
+        <v>66.7</v>
+      </c>
+      <c r="H5">
+        <v>78.8</v>
+      </c>
+      <c r="I5">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>0.3</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>6.9</v>
-      </c>
-      <c r="E5">
-        <v>71.3</v>
-      </c>
-      <c r="F5">
-        <v>87.7</v>
-      </c>
-      <c r="G5">
-        <v>85.39999999999999</v>
-      </c>
-      <c r="H5">
-        <v>86.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B6">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C6">
-        <v>6.4</v>
+        <v>10.2</v>
       </c>
       <c r="D6">
-        <v>4.7</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="E6">
-        <v>26.6</v>
+        <v>72.7</v>
       </c>
       <c r="F6">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G6">
-        <v>81.69999999999999</v>
+        <v>85</v>
       </c>
       <c r="H6">
-        <v>85.39999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>82</v>
+      </c>
+      <c r="I6">
+        <v>79.80000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="C7">
+        <v>39.8</v>
+      </c>
+      <c r="D7">
+        <v>90.8</v>
+      </c>
+      <c r="E7">
+        <v>97</v>
+      </c>
+      <c r="F7">
+        <v>64.8</v>
+      </c>
+      <c r="G7">
+        <v>52.8</v>
+      </c>
+      <c r="H7">
+        <v>78.5</v>
+      </c>
+      <c r="I7">
+        <v>79.10000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="C7">
-        <v>87</v>
-      </c>
-      <c r="D7">
-        <v>89.8</v>
-      </c>
-      <c r="E7">
-        <v>62</v>
-      </c>
-      <c r="F7">
-        <v>32.8</v>
-      </c>
-      <c r="G7">
-        <v>77.7</v>
-      </c>
-      <c r="H7">
-        <v>79.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B8">
-        <v>45.2</v>
+        <v>74.7</v>
       </c>
       <c r="C8">
-        <v>98.5</v>
+        <v>90.10000000000001</v>
       </c>
       <c r="D8">
-        <v>98.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="E8">
-        <v>81</v>
+        <v>59.3</v>
       </c>
       <c r="F8">
-        <v>89.8</v>
+        <v>29.8</v>
       </c>
       <c r="G8">
-        <v>64.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H8">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>84.89999999999999</v>
+      </c>
+      <c r="I8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -3230,178 +3318,199 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>69.3</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="D9">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="E9">
-        <v>97.39999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="F9">
-        <v>77.8</v>
+        <v>81.5</v>
       </c>
       <c r="G9">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
       <c r="H9">
-        <v>65.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>63.6</v>
+      </c>
+      <c r="I9">
+        <v>67.10000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>6.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C10">
-        <v>39</v>
+        <v>21.5</v>
       </c>
       <c r="D10">
-        <v>92.30000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="E10">
+        <v>20.8</v>
+      </c>
+      <c r="F10">
+        <v>43.7</v>
+      </c>
+      <c r="G10">
+        <v>61.1</v>
+      </c>
+      <c r="H10">
+        <v>67.80000000000001</v>
+      </c>
+      <c r="I10">
+        <v>66.40000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
         <v>96.2</v>
       </c>
-      <c r="F10">
-        <v>66.2</v>
-      </c>
-      <c r="G10">
-        <v>50.1</v>
-      </c>
-      <c r="H10">
-        <v>55.50000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>98.8</v>
-      </c>
       <c r="C11">
-        <v>25.4</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>11.5</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>21.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F11">
-        <v>43.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G11">
-        <v>63.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H11">
-        <v>53.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>52.90000000000001</v>
+      </c>
+      <c r="I11">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
-        <v>18.8</v>
+        <v>16.9</v>
       </c>
       <c r="F12">
-        <v>32.6</v>
+        <v>37.4</v>
       </c>
       <c r="G12">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="H12">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>14.9</v>
+      </c>
+      <c r="C13">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="D13">
+        <v>3.8</v>
+      </c>
+      <c r="E13">
+        <v>4.7</v>
+      </c>
+      <c r="F13">
+        <v>0.8</v>
+      </c>
+      <c r="G13">
+        <v>3.3</v>
+      </c>
+      <c r="H13">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13">
-        <v>94.89999999999999</v>
-      </c>
-      <c r="C13">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="D13">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="E13">
-        <v>15.6</v>
-      </c>
-      <c r="F13">
-        <v>2.6</v>
-      </c>
-      <c r="G13">
-        <v>3.5</v>
-      </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B14">
-        <v>14.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C14">
-        <v>1.1</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D14">
-        <v>4.399999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E14">
-        <v>3.2</v>
+        <v>16.3</v>
       </c>
       <c r="F14">
+        <v>1.8</v>
+      </c>
+      <c r="G14">
+        <v>2.4</v>
+      </c>
+      <c r="H14">
+        <v>0.3</v>
+      </c>
+      <c r="I14">
         <v>0.4</v>
       </c>
-      <c r="G14">
-        <v>3.6</v>
-      </c>
-      <c r="H14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>69.39999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="C15">
-        <v>68.89999999999999</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="D15">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>7.399999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="F15">
-        <v>1.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G15">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H15">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3416,28 +3525,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3445,28 +3554,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>105.41</v>
+        <v>103.42</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2">
-        <v>115.35</v>
+        <v>111.52</v>
       </c>
       <c r="G2">
-        <v>0.583</v>
+        <v>0.51</v>
       </c>
       <c r="H2">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3474,28 +3583,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>101.28</v>
+        <v>106.45</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>112.24</v>
+        <v>113.5</v>
       </c>
       <c r="G3">
-        <v>0.521</v>
+        <v>0.571</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9.9</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3503,28 +3612,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4">
-        <v>108.28</v>
+        <v>112.81</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>108.94</v>
+        <v>110.42</v>
       </c>
       <c r="G4">
-        <v>0.458</v>
+        <v>0.49</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3532,28 +3641,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5">
+        <v>112.45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>109.33</v>
+      </c>
+      <c r="G5">
+        <v>0.49</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
+      </c>
+      <c r="I5">
         <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5">
-        <v>112.21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>108.31</v>
-      </c>
-      <c r="G5">
-        <v>0.458</v>
-      </c>
-      <c r="H5">
-        <v>5.8</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3561,28 +3670,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6">
-        <v>85.12</v>
+        <v>99.78</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>107.95</v>
+        <v>108.54</v>
       </c>
       <c r="G6">
-        <v>0.458</v>
+        <v>0.49</v>
       </c>
       <c r="H6">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3590,28 +3699,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7">
-        <v>100.75</v>
+        <v>80.19</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>109.41</v>
+        <v>106.76</v>
       </c>
       <c r="G7">
-        <v>0.521</v>
+        <v>0.469</v>
       </c>
       <c r="H7">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3619,28 +3728,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8">
-        <v>117.44</v>
+        <v>112.66</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8">
-        <v>108.94</v>
+        <v>105.59</v>
       </c>
       <c r="G8">
-        <v>0.542</v>
+        <v>0.408</v>
       </c>
       <c r="H8">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3651,25 +3760,25 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>104.82</v>
+        <v>110.69</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9">
-        <v>105.5</v>
+        <v>105.26</v>
       </c>
       <c r="G9">
-        <v>0.438</v>
+        <v>0.469</v>
       </c>
       <c r="H9">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3680,25 +3789,25 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10">
-        <v>97.34</v>
+        <v>99.12</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10">
-        <v>105.35</v>
+        <v>105.81</v>
       </c>
       <c r="G10">
-        <v>0.521</v>
+        <v>0.551</v>
       </c>
       <c r="H10">
-        <v>-4.4</v>
+        <v>-4</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3709,25 +3818,25 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11">
-        <v>97.2</v>
+        <v>93.25</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11">
-        <v>104.84</v>
+        <v>103.01</v>
       </c>
       <c r="G11">
-        <v>0.438</v>
+        <v>0.429</v>
       </c>
       <c r="H11">
-        <v>-5</v>
+        <v>-6.1</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3738,25 +3847,25 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12">
-        <v>128.44</v>
+        <v>122.1</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
       </c>
       <c r="F12">
-        <v>107.06</v>
+        <v>107.72</v>
       </c>
       <c r="G12">
-        <v>0.583</v>
+        <v>0.612</v>
       </c>
       <c r="H12">
-        <v>-6.9</v>
+        <v>-6.7</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3764,28 +3873,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13">
-        <v>105.68</v>
+        <v>111.05</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
       </c>
       <c r="F13">
-        <v>103.98</v>
+        <v>104.02</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="H13">
-        <v>-7.2</v>
+        <v>-7.7</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3793,28 +3902,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14">
-        <v>112.89</v>
+        <v>125.66</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F14">
-        <v>102.81</v>
+        <v>102.65</v>
       </c>
       <c r="G14">
-        <v>0.458</v>
+        <v>0.531</v>
       </c>
       <c r="H14">
-        <v>-7.2</v>
+        <v>-10.3</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3822,28 +3931,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15">
-        <v>127.8</v>
+        <v>103.78</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>103.97</v>
+        <v>99.31</v>
       </c>
       <c r="G15">
-        <v>0.521</v>
+        <v>0.449</v>
       </c>
       <c r="H15">
-        <v>-8.9</v>
+        <v>-11</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3858,31 +3967,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3890,28 +3999,28 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>127.7966666666667</v>
+        <v>125.6571428571428</v>
       </c>
       <c r="E2">
-        <v>766.78</v>
+        <v>879.5999999999999</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3919,115 +4028,115 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>128.4366666666667</v>
+        <v>122.1</v>
       </c>
       <c r="E3">
-        <v>770.62</v>
+        <v>854.7</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D4">
-        <v>117.4366666666667</v>
+        <v>106.4457142857143</v>
       </c>
       <c r="E4">
-        <v>704.6200000000001</v>
+        <v>745.12</v>
       </c>
       <c r="F4">
-        <v>89.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>112.8866666666667</v>
+        <v>112.6628571428572</v>
       </c>
       <c r="E5">
-        <v>677.3199999999999</v>
+        <v>788.6400000000001</v>
       </c>
       <c r="F5">
-        <v>85.7</v>
+        <v>86.3</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C6">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6">
-        <v>105.4133333333333</v>
+        <v>111.0485714285714</v>
       </c>
       <c r="E6">
-        <v>632.48</v>
+        <v>777.3399999999999</v>
       </c>
       <c r="F6">
-        <v>82.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4035,57 +4144,57 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>112.2066666666667</v>
+        <v>112.8114285714286</v>
       </c>
       <c r="E7">
-        <v>673.24</v>
+        <v>789.6800000000001</v>
       </c>
       <c r="F7">
-        <v>81.3</v>
+        <v>77.2</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D8">
-        <v>108.2766666666667</v>
+        <v>110.6857142857143</v>
       </c>
       <c r="E8">
-        <v>649.6600000000001</v>
+        <v>774.8</v>
       </c>
       <c r="F8">
-        <v>65.10000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="G8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -4093,28 +4202,28 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D9">
-        <v>105.68</v>
+        <v>103.7771428571428</v>
       </c>
       <c r="E9">
-        <v>634.0799999999999</v>
+        <v>726.4399999999999</v>
       </c>
       <c r="F9">
-        <v>64</v>
+        <v>70.19999999999999</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4125,54 +4234,54 @@
         <v>80</v>
       </c>
       <c r="C10">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D10">
-        <v>101.2766666666667</v>
+        <v>103.42</v>
       </c>
       <c r="E10">
-        <v>607.6600000000001</v>
+        <v>723.9400000000001</v>
       </c>
       <c r="F10">
-        <v>57.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D11">
-        <v>104.8233333333333</v>
+        <v>112.4485714285714</v>
       </c>
       <c r="E11">
-        <v>628.9399999999999</v>
+        <v>787.1400000000001</v>
       </c>
       <c r="F11">
-        <v>56.99999999999999</v>
+        <v>49.8</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4180,28 +4289,28 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D12">
-        <v>100.75</v>
+        <v>99.78285714285714</v>
       </c>
       <c r="E12">
-        <v>604.5</v>
+        <v>698.48</v>
       </c>
       <c r="F12">
-        <v>12.7</v>
+        <v>3.1</v>
       </c>
       <c r="G12">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4209,28 +4318,28 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C13">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D13">
-        <v>97.33999999999999</v>
+        <v>99.11999999999999</v>
       </c>
       <c r="E13">
-        <v>584.04</v>
+        <v>693.8399999999999</v>
       </c>
       <c r="F13">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="G13">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4238,28 +4347,28 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C14">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D14">
-        <v>97.20333333333333</v>
+        <v>93.25142857142858</v>
       </c>
       <c r="E14">
-        <v>583.22</v>
+        <v>652.76</v>
       </c>
       <c r="F14">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="G14">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4267,28 +4376,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C15">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D15">
-        <v>85.11999999999999</v>
+        <v>80.19428571428571</v>
       </c>
       <c r="E15">
-        <v>510.72</v>
+        <v>561.36</v>
       </c>
       <c r="F15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>70</v>
+        <v>73.2</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I15" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4303,19 +4412,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4326,16 +4435,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4346,16 +4455,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4366,16 +4475,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4383,10 +4492,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -4395,7 +4504,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4403,19 +4512,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4423,19 +4532,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4443,19 +4552,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4463,19 +4572,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4483,19 +4592,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D10">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4506,16 +4615,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D11">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4526,16 +4635,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12">
         <v>-15</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4543,19 +4652,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4563,19 +4672,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4583,19 +4692,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D15">
         <v>-21</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4605,33 +4714,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>126</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4653,11 +4765,14 @@
       <c r="G2">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4679,11 +4794,14 @@
       <c r="G3">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -4705,167 +4823,188 @@
       <c r="G4">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>-1</v>
+      </c>
+      <c r="C5">
+        <v>-3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>-5</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>-9</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>-2</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>-3</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>-2</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>9</v>
       </c>
-      <c r="H5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>-4</v>
+      </c>
+      <c r="D7">
+        <v>-3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>-1</v>
+      </c>
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>-2</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>-3</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="D9">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="E9">
         <v>11</v>
       </c>
-      <c r="F6">
+      <c r="F9">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G9">
         <v>7</v>
       </c>
-      <c r="H6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>-1</v>
-      </c>
-      <c r="C7">
-        <v>-3</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>-4</v>
-      </c>
-      <c r="D8">
-        <v>-3</v>
-      </c>
-      <c r="E8">
+      <c r="I9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
         <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>-7</v>
-      </c>
-      <c r="F9">
-        <v>-7</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>-1</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="G10">
-        <v>-3</v>
-      </c>
-      <c r="H10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>-6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -4887,11 +5026,14 @@
       <c r="G11">
         <v>-6</v>
       </c>
-      <c r="H11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11">
+        <v>-10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -4913,86 +5055,98 @@
       <c r="G12">
         <v>-15</v>
       </c>
-      <c r="H12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="H12">
+        <v>-15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>-4</v>
+      </c>
+      <c r="D13">
+        <v>-15</v>
+      </c>
+      <c r="E13">
+        <v>-16</v>
+      </c>
+      <c r="F13">
+        <v>-16</v>
+      </c>
+      <c r="G13">
+        <v>-21</v>
+      </c>
+      <c r="H13">
+        <v>-19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>-4</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>-9</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>-17</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>-17</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>-15</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>-18</v>
       </c>
-      <c r="H13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
+      <c r="H14">
+        <v>-20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>-3</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>-1</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>-3</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>-6</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>-12</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>-19</v>
       </c>
-      <c r="H14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>-4</v>
-      </c>
-      <c r="D15">
-        <v>-15</v>
-      </c>
-      <c r="E15">
-        <v>-16</v>
-      </c>
-      <c r="F15">
-        <v>-16</v>
-      </c>
-      <c r="G15">
+      <c r="H15">
         <v>-21</v>
       </c>
-      <c r="H15" t="s">
-        <v>112</v>
+      <c r="I15" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/THE BEST OF THE BEST 2026.xlsx
+++ b/data/leagues/THE BEST OF THE BEST 2026.xlsx
@@ -283,19 +283,22 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>10.4-3.5-0.1</t>
-  </si>
-  <si>
-    <t>9.8-4.2-0.1</t>
+    <t>10.3-3.7-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
   </si>
   <si>
     <t>8.9-5.0-0.1</t>
   </si>
   <si>
-    <t>8.1-5.9-0.1</t>
-  </si>
-  <si>
-    <t>8.0-6.0-0.1</t>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.0-0.1</t>
   </si>
   <si>
     <t>7.7-6.2-0.1</t>
@@ -304,19 +307,19 @@
     <t>7.8-6.1-0.1</t>
   </si>
   <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.2-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.2-0.1</t>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>3.7-10.2-0.1</t>
   </si>
   <si>
     <t>3.6-10.3-0.1</t>
   </si>
   <si>
-    <t>2.5-11.5-0.1</t>
+    <t>2.4-11.5-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -338,9 +341,6 @@
   </si>
   <si>
     <t>4-10</t>
-  </si>
-  <si>
-    <t>3-11</t>
   </si>
   <si>
     <t>2-12</t>
@@ -2376,35 +2376,35 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>58.3</v>
+        <v>55.7</v>
       </c>
       <c r="C2">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="D2">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E2">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H2">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I2">
+        <v>0.7</v>
+      </c>
+      <c r="J2">
         <v>0.2</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.1</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
         <v>0</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2426,37 +2426,37 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="D3">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="E3">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="F3">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="G3">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="I3">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -2476,37 +2476,37 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="C4">
-        <v>12.9</v>
+        <v>11.2</v>
       </c>
       <c r="D4">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="E4">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F4">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>10.8</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>90.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2526,49 +2526,49 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>12.7</v>
       </c>
       <c r="F5">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="H5">
+        <v>9.4</v>
+      </c>
+      <c r="I5">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J5">
         <v>10.7</v>
       </c>
-      <c r="I5">
-        <v>10.8</v>
-      </c>
-      <c r="J5">
-        <v>7.1</v>
-      </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="L5">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="M5">
+        <v>0.1</v>
+      </c>
+      <c r="N5">
         <v>0.2</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>86.3</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2576,190 +2576,190 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="C6">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="D6">
-        <v>13.9</v>
+        <v>12.3</v>
       </c>
       <c r="E6">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="F6">
         <v>11.3</v>
       </c>
       <c r="G6">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H6">
-        <v>9.9</v>
+        <v>13.3</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="K6">
-        <v>9.9</v>
+        <v>8.6</v>
       </c>
       <c r="L6">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>78.5</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>1.5</v>
       </c>
       <c r="C7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D7">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="F7">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="G7">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="H7">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="I7">
-        <v>13.4</v>
+        <v>12.3</v>
       </c>
       <c r="J7">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="K7">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>77.2</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="C8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D8">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E8">
+        <v>10.2</v>
+      </c>
+      <c r="F8">
+        <v>12.7</v>
+      </c>
+      <c r="G8">
+        <v>15.2</v>
+      </c>
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="F8">
-        <v>11.7</v>
-      </c>
-      <c r="G8">
-        <v>11.9</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
       <c r="I8">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="J8">
-        <v>10.5</v>
+        <v>13.1</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="L8">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M8">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>76.8</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="D9">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
       <c r="E9">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="F9">
+        <v>11.4</v>
+      </c>
+      <c r="G9">
+        <v>10.1</v>
+      </c>
+      <c r="H9">
+        <v>12.3</v>
+      </c>
+      <c r="I9">
+        <v>15.6</v>
+      </c>
+      <c r="J9">
+        <v>15.3</v>
+      </c>
+      <c r="K9">
         <v>11.7</v>
       </c>
-      <c r="G9">
-        <v>10.4</v>
-      </c>
-      <c r="H9">
-        <v>13.1</v>
-      </c>
-      <c r="I9">
-        <v>14.6</v>
-      </c>
-      <c r="J9">
-        <v>13.3</v>
-      </c>
-      <c r="K9">
-        <v>10.5</v>
-      </c>
       <c r="L9">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -2768,48 +2768,48 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>70.2</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="C10">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D10">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="E10">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G10">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="H10">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="I10">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="J10">
-        <v>15.5</v>
+        <v>12.9</v>
       </c>
       <c r="K10">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="L10">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="M10">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2826,49 +2826,49 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D11">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="E11">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="F11">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H11">
-        <v>10.7</v>
+        <v>13.2</v>
       </c>
       <c r="I11">
-        <v>13.9</v>
+        <v>14.8</v>
       </c>
       <c r="J11">
-        <v>19.8</v>
+        <v>14.3</v>
       </c>
       <c r="K11">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="L11">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="N11">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>49.8</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2888,37 +2888,37 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="I12">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J12">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K12">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="L12">
-        <v>43.9</v>
+        <v>44.7</v>
       </c>
       <c r="M12">
         <v>22.3</v>
       </c>
       <c r="N12">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="O12">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2944,31 +2944,31 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J13">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <v>17.2</v>
       </c>
       <c r="M13">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="N13">
-        <v>25.1</v>
+        <v>27.1</v>
       </c>
       <c r="O13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2991,34 +2991,34 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H14">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I14">
+        <v>0.2</v>
+      </c>
+      <c r="J14">
+        <v>0.6</v>
+      </c>
+      <c r="K14">
+        <v>3.2</v>
+      </c>
+      <c r="L14">
+        <v>14.1</v>
+      </c>
+      <c r="M14">
+        <v>24.3</v>
+      </c>
+      <c r="N14">
+        <v>41.8</v>
+      </c>
+      <c r="O14">
+        <v>15.7</v>
+      </c>
+      <c r="P14">
         <v>0.3</v>
-      </c>
-      <c r="J14">
-        <v>0.9</v>
-      </c>
-      <c r="K14">
-        <v>2.9</v>
-      </c>
-      <c r="L14">
-        <v>12.3</v>
-      </c>
-      <c r="M14">
-        <v>25.2</v>
-      </c>
-      <c r="N14">
-        <v>43</v>
-      </c>
-      <c r="O14">
-        <v>15.3</v>
-      </c>
-      <c r="P14">
-        <v>0.4</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3056,19 +3056,19 @@
         <v>0.1</v>
       </c>
       <c r="L15">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M15">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="N15">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="O15">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3121,7 +3121,7 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -3133,7 +3133,7 @@
         <v>99.8</v>
       </c>
       <c r="I2">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3150,19 +3150,19 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F3">
         <v>100</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H3">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I3">
-        <v>98.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3170,28 +3170,28 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C4">
-        <v>9.700000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D4">
-        <v>6.1</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="E4">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="F4">
-        <v>70.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G4">
-        <v>80.5</v>
+        <v>80.10000000000001</v>
       </c>
       <c r="H4">
-        <v>88.3</v>
+        <v>87.3</v>
       </c>
       <c r="I4">
-        <v>91.5</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3199,28 +3199,28 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>42.4</v>
+        <v>45.5</v>
       </c>
       <c r="C5">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="D5">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="E5">
-        <v>80.5</v>
+        <v>81.39999999999999</v>
       </c>
       <c r="F5">
-        <v>89.3</v>
+        <v>90</v>
       </c>
       <c r="G5">
-        <v>66.7</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="H5">
-        <v>78.8</v>
+        <v>75.7</v>
       </c>
       <c r="I5">
-        <v>83.8</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3228,86 +3228,86 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C6">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="D6">
-        <v>5.899999999999999</v>
+        <v>7.399999999999999</v>
       </c>
       <c r="E6">
-        <v>72.7</v>
+        <v>72.39999999999999</v>
       </c>
       <c r="F6">
-        <v>86.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="G6">
-        <v>85</v>
+        <v>85.3</v>
       </c>
       <c r="H6">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="I6">
-        <v>79.80000000000001</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>5.600000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C7">
-        <v>39.8</v>
+        <v>87</v>
       </c>
       <c r="D7">
-        <v>90.8</v>
+        <v>91.8</v>
       </c>
       <c r="E7">
-        <v>97</v>
+        <v>57.9</v>
       </c>
       <c r="F7">
-        <v>64.8</v>
+        <v>30.8</v>
       </c>
       <c r="G7">
-        <v>52.8</v>
+        <v>78.5</v>
       </c>
       <c r="H7">
-        <v>78.5</v>
+        <v>84.3</v>
       </c>
       <c r="I7">
-        <v>79.10000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>74.7</v>
+        <v>5.7</v>
       </c>
       <c r="C8">
-        <v>90.10000000000001</v>
+        <v>41.9</v>
       </c>
       <c r="D8">
-        <v>90.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E8">
-        <v>59.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F8">
-        <v>29.8</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>79.5</v>
+        <v>52.3</v>
       </c>
       <c r="H8">
-        <v>84.89999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="I8">
-        <v>79</v>
+        <v>77.60000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3318,25 +3318,25 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>67.30000000000001</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="D9">
-        <v>98.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E9">
-        <v>97.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F9">
-        <v>81.5</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="G9">
-        <v>61.1</v>
+        <v>63</v>
       </c>
       <c r="H9">
-        <v>63.6</v>
+        <v>63.3</v>
       </c>
       <c r="I9">
-        <v>67.10000000000001</v>
+        <v>68.10000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3344,28 +3344,28 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>99.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="C10">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D10">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="E10">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="F10">
-        <v>43.7</v>
+        <v>46.2</v>
       </c>
       <c r="G10">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="H10">
-        <v>67.80000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I10">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3373,7 +3373,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>96.2</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3382,19 +3382,19 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F11">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="G11">
-        <v>89.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H11">
-        <v>52.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="I11">
-        <v>50.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3402,28 +3402,28 @@
         <v>8</v>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.1</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
       <c r="D12">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E12">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="F12">
-        <v>37.4</v>
+        <v>33</v>
       </c>
       <c r="G12">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3431,28 +3431,28 @@
         <v>4</v>
       </c>
       <c r="B13">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="C13">
-        <v>0.7000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="D13">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="E13">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="F13">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="H13">
-        <v>0.8999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3460,25 +3460,25 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <v>94.09999999999999</v>
+        <v>94.69999999999999</v>
       </c>
       <c r="C14">
-        <v>94.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="D14">
-        <v>70.5</v>
+        <v>66.3</v>
       </c>
       <c r="E14">
-        <v>16.3</v>
+        <v>18.8</v>
       </c>
       <c r="F14">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G14">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I14">
         <v>0.4</v>
@@ -3489,28 +3489,28 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>71.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C15">
-        <v>67.30000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="E15">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="F15">
-        <v>0.8999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4011,7 +4011,7 @@
         <v>879.5999999999999</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4049,7 +4049,7 @@
         <v>87</v>
       </c>
       <c r="I3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4069,7 +4069,7 @@
         <v>745.12</v>
       </c>
       <c r="F4">
-        <v>90.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4078,7 +4078,7 @@
         <v>88</v>
       </c>
       <c r="I4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4098,7 +4098,7 @@
         <v>788.6400000000001</v>
       </c>
       <c r="F5">
-        <v>86.3</v>
+        <v>82.3</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>89</v>
       </c>
       <c r="I5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4127,7 +4127,7 @@
         <v>777.3399999999999</v>
       </c>
       <c r="F6">
-        <v>78.5</v>
+        <v>78.10000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4136,12 +4136,12 @@
         <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>82</v>
@@ -4150,13 +4150,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>112.8114285714286</v>
+        <v>110.6857142857143</v>
       </c>
       <c r="E7">
-        <v>789.6800000000001</v>
+        <v>774.8</v>
       </c>
       <c r="F7">
-        <v>77.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
@@ -4179,13 +4179,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D8">
-        <v>110.6857142857143</v>
+        <v>112.8114285714286</v>
       </c>
       <c r="E8">
-        <v>774.8</v>
+        <v>789.6800000000001</v>
       </c>
       <c r="F8">
-        <v>76.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4194,65 +4194,65 @@
         <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D9">
-        <v>103.7771428571428</v>
+        <v>103.42</v>
       </c>
       <c r="E9">
-        <v>726.4399999999999</v>
+        <v>723.9400000000001</v>
       </c>
       <c r="F9">
-        <v>70.19999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D10">
-        <v>103.42</v>
+        <v>103.7771428571428</v>
       </c>
       <c r="E10">
-        <v>723.9400000000001</v>
+        <v>726.4399999999999</v>
       </c>
       <c r="F10">
-        <v>67.90000000000001</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4272,16 +4272,16 @@
         <v>787.1400000000001</v>
       </c>
       <c r="F11">
-        <v>49.8</v>
+        <v>56.10000000000001</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4301,16 +4301,16 @@
         <v>698.48</v>
       </c>
       <c r="F12">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="G12">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4330,16 +4330,16 @@
         <v>693.8399999999999</v>
       </c>
       <c r="F13">
-        <v>0.5</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4359,13 +4359,13 @@
         <v>652.76</v>
       </c>
       <c r="F14">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G14">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" t="s">
         <v>105</v>
@@ -4388,13 +4388,13 @@
         <v>561.36</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G15">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="H15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
         <v>106</v>
